--- a/Gerard i Òscar/PF_ÒscarLosada_GerardMoreno_M1.xlsx
+++ b/Gerard i Òscar/PF_ÒscarLosada_GerardMoreno_M1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10309"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uab-my.sharepoint.com/personal/1598367_uab_cat/Documents/5è CURS/LACE/Lab LACE - Gerard i Òscar/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/deumenec/Documents/Uni/LACE/Gerard i Òscar/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4073" documentId="8_{47B1077E-2795-674F-807F-93E5B295736B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9AD6B4EA-F6A3-4D15-9739-744209A285F6}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66D4B36C-79A1-AA45-999A-F453825CBE84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{C1122783-245A-4FED-BDEB-F09B1698DCDF}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" xr2:uid="{C1122783-245A-4FED-BDEB-F09B1698DCDF}"/>
   </bookViews>
   <sheets>
     <sheet name="Pràctica A" sheetId="1" r:id="rId1"/>
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -91,7 +91,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="170">
   <si>
     <t>Data:</t>
   </si>
@@ -2219,22 +2219,7 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2245,15 +2230,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2273,13 +2249,37 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2302,7 +2302,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -3093,7 +3093,7 @@
 <file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -3741,7 +3741,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -4789,7 +4789,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -5580,7 +5580,7 @@
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -6215,7 +6215,7 @@
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -6850,7 +6850,7 @@
 <file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -7427,7 +7427,7 @@
 <file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -8246,7 +8246,7 @@
 <file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -8544,49 +8544,49 @@
                 <c:formatCode>0.000000</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>0.2226919573709486</c:v>
+                  <c:v>0.22269195737094863</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.24272440307632859</c:v>
+                  <c:v>0.24272440307632862</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.27130480648743699</c:v>
+                  <c:v>0.27130480648743704</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.29152802369432668</c:v>
+                  <c:v>0.29152802369432673</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.30313318921691107</c:v>
+                  <c:v>0.30313318921691113</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.30626516476532445</c:v>
+                  <c:v>0.3062651647653245</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.30543569211847821</c:v>
+                  <c:v>0.30543569211847826</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.30496993009569001</c:v>
+                  <c:v>0.30496993009569007</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.30456400878169759</c:v>
+                  <c:v>0.30456400878169765</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.30212279136726888</c:v>
+                  <c:v>0.30212279136726894</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.29558648814795901</c:v>
+                  <c:v>0.29558648814795907</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.28366528932379464</c:v>
+                  <c:v>0.2836652893237947</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.26621367765269421</c:v>
+                  <c:v>0.26621367765269427</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.24522637501843633</c:v>
+                  <c:v>0.24522637501843636</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.22307622735932153</c:v>
+                  <c:v>0.22307622735932156</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8888,7 +8888,7 @@
 <file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -16272,15 +16272,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{953B08C8-5267-41A1-8A30-44F36ECBD8D8}">
   <dimension ref="A1:R267"/>
-  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="23.25" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="23.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="28.44140625" style="2" customWidth="1"/>
+    <col min="1" max="1" width="28.5" style="2" customWidth="1"/>
     <col min="2" max="3" width="27" style="2" customWidth="1"/>
     <col min="4" max="10" width="24.33203125" style="2" customWidth="1"/>
-    <col min="11" max="16384" width="11.44140625" style="2"/>
+    <col min="11" max="16384" width="11.5" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>7</v>
       </c>
@@ -16291,7 +16291,7 @@
         <v>45776</v>
       </c>
     </row>
-    <row r="2" spans="1:6" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
@@ -16305,7 +16305,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="3" spans="1:6" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>3</v>
       </c>
@@ -16313,93 +16313,93 @@
         <v>61</v>
       </c>
     </row>
-    <row r="4" spans="1:6" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="4"/>
     </row>
-    <row r="5" spans="1:6" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="115" t="s">
+    <row r="6" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="125" t="s">
         <v>74</v>
       </c>
-      <c r="B6" s="116"/>
-      <c r="C6" s="116"/>
-      <c r="D6" s="116"/>
-    </row>
-    <row r="7" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="116"/>
-      <c r="B7" s="116"/>
-      <c r="C7" s="116"/>
-      <c r="D7" s="116"/>
-    </row>
-    <row r="8" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="116"/>
-      <c r="B8" s="116"/>
-      <c r="C8" s="116"/>
-      <c r="D8" s="116"/>
-    </row>
-    <row r="9" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="126"/>
+      <c r="C6" s="126"/>
+      <c r="D6" s="126"/>
+    </row>
+    <row r="7" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="126"/>
+      <c r="B7" s="126"/>
+      <c r="C7" s="126"/>
+      <c r="D7" s="126"/>
+    </row>
+    <row r="8" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="126"/>
+      <c r="B8" s="126"/>
+      <c r="C8" s="126"/>
+      <c r="D8" s="126"/>
+    </row>
+    <row r="9" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="115" t="s">
+    <row r="10" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="125" t="s">
         <v>69</v>
       </c>
-      <c r="B10" s="115"/>
-      <c r="C10" s="115"/>
-      <c r="D10" s="115"/>
-    </row>
-    <row r="11" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="115"/>
-      <c r="B11" s="115"/>
-      <c r="C11" s="115"/>
-      <c r="D11" s="115"/>
-    </row>
-    <row r="12" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="115"/>
-      <c r="B12" s="115"/>
-      <c r="C12" s="115"/>
-      <c r="D12" s="115"/>
-    </row>
-    <row r="13" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="115"/>
-      <c r="B13" s="115"/>
-      <c r="C13" s="115"/>
-      <c r="D13" s="115"/>
-    </row>
-    <row r="14" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="115"/>
-      <c r="B14" s="115"/>
-      <c r="C14" s="115"/>
-      <c r="D14" s="115"/>
-    </row>
-    <row r="15" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="115"/>
-      <c r="B15" s="115"/>
-      <c r="C15" s="115"/>
-      <c r="D15" s="115"/>
-    </row>
-    <row r="17" spans="1:4" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="125"/>
+      <c r="C10" s="125"/>
+      <c r="D10" s="125"/>
+    </row>
+    <row r="11" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="125"/>
+      <c r="B11" s="125"/>
+      <c r="C11" s="125"/>
+      <c r="D11" s="125"/>
+    </row>
+    <row r="12" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="125"/>
+      <c r="B12" s="125"/>
+      <c r="C12" s="125"/>
+      <c r="D12" s="125"/>
+    </row>
+    <row r="13" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="125"/>
+      <c r="B13" s="125"/>
+      <c r="C13" s="125"/>
+      <c r="D13" s="125"/>
+    </row>
+    <row r="14" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="125"/>
+      <c r="B14" s="125"/>
+      <c r="C14" s="125"/>
+      <c r="D14" s="125"/>
+    </row>
+    <row r="15" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="125"/>
+      <c r="B15" s="125"/>
+      <c r="C15" s="125"/>
+      <c r="D15" s="125"/>
+    </row>
+    <row r="17" spans="1:4" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B17" s="124" t="s">
+      <c r="B17" s="131" t="s">
         <v>75</v>
       </c>
-      <c r="C17" s="125"/>
-      <c r="D17" s="125"/>
-    </row>
-    <row r="18" spans="1:4" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="124"/>
-      <c r="C18" s="125"/>
-      <c r="D18" s="125"/>
-    </row>
-    <row r="19" spans="1:4" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C17" s="132"/>
+      <c r="D17" s="132"/>
+    </row>
+    <row r="18" spans="1:4" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B18" s="131"/>
+      <c r="C18" s="132"/>
+      <c r="D18" s="132"/>
+    </row>
+    <row r="19" spans="1:4" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>8</v>
       </c>
@@ -16410,7 +16410,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>14</v>
       </c>
@@ -16421,7 +16421,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>13</v>
       </c>
@@ -16432,7 +16432,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>9</v>
       </c>
@@ -16443,7 +16443,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>10</v>
       </c>
@@ -16454,7 +16454,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>11</v>
       </c>
@@ -16465,17 +16465,17 @@
         <v>67</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B26" s="17"/>
       <c r="C26" s="17"/>
       <c r="D26" s="17"/>
     </row>
-    <row r="27" spans="1:4" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="4" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
         <v>8</v>
       </c>
@@ -16486,7 +16486,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
         <v>14</v>
       </c>
@@ -16497,7 +16497,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="32" spans="1:4" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
         <v>16</v>
       </c>
@@ -16508,7 +16508,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:5" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
         <v>9</v>
       </c>
@@ -16519,7 +16519,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="34" spans="1:5" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:5" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
         <v>10</v>
       </c>
@@ -16530,7 +16530,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:5" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
         <v>11</v>
       </c>
@@ -16541,20 +16541,20 @@
         <v>67</v>
       </c>
     </row>
-    <row r="36" spans="1:5" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:5" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B36" s="17"/>
       <c r="C36" s="17"/>
     </row>
-    <row r="37" spans="1:5" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:5" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B37" s="17"/>
       <c r="C37" s="17"/>
     </row>
-    <row r="38" spans="1:5" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:5" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="4" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:5" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="7" t="s">
         <v>23</v>
       </c>
@@ -16565,7 +16565,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:5" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="7" t="s">
         <v>24</v>
       </c>
@@ -16576,7 +16576,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:5" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
         <v>19</v>
       </c>
@@ -16593,7 +16593,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:5" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
         <v>20</v>
       </c>
@@ -16610,7 +16610,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="45" spans="1:5" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:5" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
         <v>21</v>
       </c>
@@ -16627,7 +16627,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="46" spans="1:5" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:5" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
         <v>22</v>
       </c>
@@ -16644,41 +16644,41 @@
         <v>67</v>
       </c>
     </row>
-    <row r="47" spans="1:5" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:5" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B47" s="17"/>
       <c r="C47" s="17"/>
     </row>
-    <row r="48" spans="1:5" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:5" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B48" s="17"/>
       <c r="C48" s="17"/>
     </row>
-    <row r="49" spans="1:12" ht="37.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:12" ht="38" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="4" t="s">
         <v>37</v>
       </c>
       <c r="D49" s="53"/>
     </row>
-    <row r="50" spans="1:12" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:12" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="4"/>
     </row>
-    <row r="51" spans="1:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B51" s="121" t="s">
+    <row r="51" spans="1:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B51" s="116" t="s">
         <v>28</v>
       </c>
-      <c r="C51" s="122"/>
-      <c r="D51" s="123"/>
-      <c r="E51" s="121" t="s">
+      <c r="C51" s="117"/>
+      <c r="D51" s="118"/>
+      <c r="E51" s="116" t="s">
         <v>29</v>
       </c>
-      <c r="F51" s="122"/>
-      <c r="G51" s="123"/>
-      <c r="H51" s="121" t="s">
+      <c r="F51" s="117"/>
+      <c r="G51" s="118"/>
+      <c r="H51" s="116" t="s">
         <v>114</v>
       </c>
-      <c r="I51" s="122"/>
-      <c r="J51" s="123"/>
-    </row>
-    <row r="52" spans="1:12" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="I51" s="117"/>
+      <c r="J51" s="118"/>
+    </row>
+    <row r="52" spans="1:12" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A52" s="7" t="s">
         <v>27</v>
       </c>
@@ -16710,7 +16710,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="53" spans="1:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="25">
         <v>550</v>
       </c>
@@ -16743,7 +16743,7 @@
       </c>
       <c r="L53" s="81"/>
     </row>
-    <row r="54" spans="1:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="26">
         <v>545</v>
       </c>
@@ -16776,7 +16776,7 @@
       </c>
       <c r="L54" s="81"/>
     </row>
-    <row r="55" spans="1:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="26">
         <v>540</v>
       </c>
@@ -16809,7 +16809,7 @@
       </c>
       <c r="L55" s="81"/>
     </row>
-    <row r="56" spans="1:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="26">
         <v>535</v>
       </c>
@@ -16842,7 +16842,7 @@
       </c>
       <c r="L56" s="81"/>
     </row>
-    <row r="57" spans="1:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="26">
         <v>530</v>
       </c>
@@ -16875,7 +16875,7 @@
       </c>
       <c r="L57" s="81"/>
     </row>
-    <row r="58" spans="1:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="26">
         <v>525</v>
       </c>
@@ -16908,7 +16908,7 @@
       </c>
       <c r="L58" s="81"/>
     </row>
-    <row r="59" spans="1:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="26">
         <v>520</v>
       </c>
@@ -16941,7 +16941,7 @@
       </c>
       <c r="L59" s="81"/>
     </row>
-    <row r="60" spans="1:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="26">
         <v>515</v>
       </c>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="L60" s="81"/>
     </row>
-    <row r="61" spans="1:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="26">
         <v>510</v>
       </c>
@@ -17007,7 +17007,7 @@
       </c>
       <c r="L61" s="81"/>
     </row>
-    <row r="62" spans="1:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="26">
         <v>505</v>
       </c>
@@ -17040,7 +17040,7 @@
       </c>
       <c r="L62" s="81"/>
     </row>
-    <row r="63" spans="1:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="26">
         <v>500</v>
       </c>
@@ -17073,7 +17073,7 @@
       </c>
       <c r="L63" s="81"/>
     </row>
-    <row r="64" spans="1:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="26">
         <v>495</v>
       </c>
@@ -17106,7 +17106,7 @@
       </c>
       <c r="L64" s="81"/>
     </row>
-    <row r="65" spans="1:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="26">
         <v>490</v>
       </c>
@@ -17139,7 +17139,7 @@
       </c>
       <c r="L65" s="81"/>
     </row>
-    <row r="66" spans="1:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="26">
         <v>485</v>
       </c>
@@ -17172,7 +17172,7 @@
       </c>
       <c r="L66" s="82"/>
     </row>
-    <row r="67" spans="1:18" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:18" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A67" s="27">
         <v>480</v>
       </c>
@@ -17205,12 +17205,12 @@
       </c>
       <c r="L67" s="81"/>
     </row>
-    <row r="68" spans="1:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B68" s="17"/>
       <c r="C68" s="17"/>
       <c r="D68" s="17"/>
     </row>
-    <row r="69" spans="1:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="6" t="s">
         <v>38</v>
       </c>
@@ -17218,7 +17218,7 @@
       <c r="C69" s="17"/>
       <c r="D69" s="17"/>
     </row>
-    <row r="71" spans="1:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="19" t="s">
         <v>30</v>
       </c>
@@ -17229,7 +17229,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="72" spans="1:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="13"/>
       <c r="B72" s="14"/>
       <c r="C72" s="14"/>
@@ -17247,7 +17247,7 @@
       <c r="Q72" s="14"/>
       <c r="R72" s="15"/>
     </row>
-    <row r="73" spans="1:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="9"/>
       <c r="D73" s="10"/>
       <c r="F73" s="9"/>
@@ -17255,7 +17255,7 @@
       <c r="M73" s="9"/>
       <c r="R73" s="10"/>
     </row>
-    <row r="74" spans="1:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="9"/>
       <c r="D74" s="10"/>
       <c r="F74" s="9"/>
@@ -17263,7 +17263,7 @@
       <c r="M74" s="9"/>
       <c r="R74" s="10"/>
     </row>
-    <row r="75" spans="1:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="9"/>
       <c r="D75" s="10"/>
       <c r="F75" s="9"/>
@@ -17271,7 +17271,7 @@
       <c r="M75" s="9"/>
       <c r="R75" s="10"/>
     </row>
-    <row r="76" spans="1:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="9"/>
       <c r="B76" s="2" t="s">
         <v>65</v>
@@ -17285,7 +17285,7 @@
       <c r="M76" s="9"/>
       <c r="R76" s="10"/>
     </row>
-    <row r="77" spans="1:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="9"/>
       <c r="B77" s="2" t="s">
         <v>66</v>
@@ -17299,7 +17299,7 @@
       <c r="M77" s="9"/>
       <c r="R77" s="10"/>
     </row>
-    <row r="78" spans="1:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="9"/>
       <c r="D78" s="10"/>
       <c r="F78" s="9"/>
@@ -17307,7 +17307,7 @@
       <c r="M78" s="9"/>
       <c r="R78" s="10"/>
     </row>
-    <row r="79" spans="1:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="9"/>
       <c r="D79" s="10"/>
       <c r="F79" s="9"/>
@@ -17315,7 +17315,7 @@
       <c r="M79" s="9"/>
       <c r="R79" s="10"/>
     </row>
-    <row r="80" spans="1:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="9"/>
       <c r="D80" s="10"/>
       <c r="F80" s="9"/>
@@ -17323,7 +17323,7 @@
       <c r="M80" s="9"/>
       <c r="R80" s="10"/>
     </row>
-    <row r="81" spans="1:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="9"/>
       <c r="D81" s="10"/>
       <c r="F81" s="9"/>
@@ -17331,7 +17331,7 @@
       <c r="M81" s="9"/>
       <c r="R81" s="10"/>
     </row>
-    <row r="82" spans="1:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="9"/>
       <c r="D82" s="10"/>
       <c r="F82" s="9"/>
@@ -17339,7 +17339,7 @@
       <c r="M82" s="9"/>
       <c r="R82" s="10"/>
     </row>
-    <row r="83" spans="1:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="8"/>
       <c r="B83" s="11"/>
       <c r="C83" s="11"/>
@@ -17357,43 +17357,43 @@
       <c r="Q83" s="11"/>
       <c r="R83" s="12"/>
     </row>
-    <row r="85" spans="1:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="B85" s="117" t="s">
+      <c r="B85" s="127" t="s">
         <v>59</v>
       </c>
-      <c r="C85" s="117"/>
-      <c r="D85" s="117"/>
-      <c r="E85" s="117"/>
-      <c r="F85" s="118"/>
-    </row>
-    <row r="86" spans="1:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C85" s="127"/>
+      <c r="D85" s="127"/>
+      <c r="E85" s="127"/>
+      <c r="F85" s="128"/>
+    </row>
+    <row r="86" spans="1:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="8"/>
-      <c r="B86" s="119"/>
-      <c r="C86" s="119"/>
-      <c r="D86" s="119"/>
-      <c r="E86" s="119"/>
-      <c r="F86" s="120"/>
-    </row>
-    <row r="88" spans="1:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B86" s="129"/>
+      <c r="C86" s="129"/>
+      <c r="D86" s="129"/>
+      <c r="E86" s="129"/>
+      <c r="F86" s="130"/>
+    </row>
+    <row r="88" spans="1:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="6" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="90" spans="1:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="6" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="91" spans="1:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="6"/>
     </row>
-    <row r="92" spans="1:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="6"/>
     </row>
-    <row r="93" spans="1:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="6" t="s">
         <v>43</v>
       </c>
@@ -17401,7 +17401,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="94" spans="1:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B94" s="67" t="s">
         <v>28</v>
       </c>
@@ -17420,7 +17420,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="95" spans="1:18" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:18" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A95" s="52" t="s">
         <v>27</v>
       </c>
@@ -17461,7 +17461,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="96" spans="1:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="63">
         <v>550</v>
       </c>
@@ -17519,24 +17519,24 @@
         <v>151</v>
       </c>
     </row>
-    <row r="97" spans="1:17" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:17" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="64">
         <v>545</v>
       </c>
       <c r="B97" s="66">
-        <f t="shared" ref="B97:B110" si="5">B54/$B$52</f>
+        <f>B54/$B$52</f>
         <v>0.39119333333333334</v>
       </c>
       <c r="C97" s="66">
-        <f t="shared" ref="C97:C110" si="6">C54/$C$52</f>
+        <f t="shared" ref="C97:C110" si="5">C54/$C$52</f>
         <v>0.39060249999999996</v>
       </c>
       <c r="D97" s="66">
-        <f t="shared" ref="D97:D110" si="7">D54/$D$52</f>
+        <f t="shared" ref="D97:D110" si="6">D54/$D$52</f>
         <v>0.41039399999999998</v>
       </c>
       <c r="E97" s="59">
-        <f t="shared" ref="E97:E109" si="8">AVERAGE(B97:D97)</f>
+        <f t="shared" ref="E97:E109" si="7">AVERAGE(B97:D97)</f>
         <v>0.39739661111111108</v>
       </c>
       <c r="F97" s="59">
@@ -17577,24 +17577,24 @@
         <v>150</v>
       </c>
     </row>
-    <row r="98" spans="1:17" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:17" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="64">
         <v>540</v>
       </c>
       <c r="B98" s="66">
+        <f t="shared" ref="B97:B110" si="8">B55/$B$52</f>
+        <v>0.40378333333333338</v>
+      </c>
+      <c r="C98" s="66">
         <f t="shared" si="5"/>
-        <v>0.40378333333333338</v>
-      </c>
-      <c r="C98" s="66">
+        <v>0.40245749999999997</v>
+      </c>
+      <c r="D98" s="66">
         <f t="shared" si="6"/>
-        <v>0.40245749999999997</v>
-      </c>
-      <c r="D98" s="66">
+        <v>0.42314000000000002</v>
+      </c>
+      <c r="E98" s="59">
         <f t="shared" si="7"/>
-        <v>0.42314000000000002</v>
-      </c>
-      <c r="E98" s="59">
-        <f t="shared" si="8"/>
         <v>0.40979361111111112</v>
       </c>
       <c r="F98" s="59">
@@ -17635,24 +17635,24 @@
         <v>151</v>
       </c>
     </row>
-    <row r="99" spans="1:17" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:17" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="64">
         <v>535</v>
       </c>
       <c r="B99" s="66">
+        <f t="shared" si="8"/>
+        <v>0.41260000000000002</v>
+      </c>
+      <c r="C99" s="66">
         <f t="shared" si="5"/>
-        <v>0.41260000000000002</v>
-      </c>
-      <c r="C99" s="66">
+        <v>0.41067999999999999</v>
+      </c>
+      <c r="D99" s="66">
         <f t="shared" si="6"/>
-        <v>0.41067999999999999</v>
-      </c>
-      <c r="D99" s="66">
+        <v>0.43226999999999999</v>
+      </c>
+      <c r="E99" s="59">
         <f t="shared" si="7"/>
-        <v>0.43226999999999999</v>
-      </c>
-      <c r="E99" s="59">
-        <f t="shared" si="8"/>
         <v>0.41851666666666665</v>
       </c>
       <c r="F99" s="59">
@@ -17693,24 +17693,24 @@
         <v>151</v>
       </c>
     </row>
-    <row r="100" spans="1:17" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:17" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="64">
         <v>530</v>
       </c>
       <c r="B100" s="66">
+        <f t="shared" si="8"/>
+        <v>0.41920333333333337</v>
+      </c>
+      <c r="C100" s="66">
         <f t="shared" si="5"/>
-        <v>0.41920333333333337</v>
-      </c>
-      <c r="C100" s="66">
+        <v>0.41595499999999996</v>
+      </c>
+      <c r="D100" s="66">
         <f t="shared" si="6"/>
-        <v>0.41595499999999996</v>
-      </c>
-      <c r="D100" s="66">
+        <v>0.43824999999999997</v>
+      </c>
+      <c r="E100" s="59">
         <f t="shared" si="7"/>
-        <v>0.43824999999999997</v>
-      </c>
-      <c r="E100" s="59">
-        <f t="shared" si="8"/>
         <v>0.4244694444444444</v>
       </c>
       <c r="F100" s="59">
@@ -17751,24 +17751,24 @@
         <v>151</v>
       </c>
     </row>
-    <row r="101" spans="1:17" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:17" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="64">
         <v>525</v>
       </c>
       <c r="B101" s="66">
+        <f t="shared" si="8"/>
+        <v>0.42255999999999999</v>
+      </c>
+      <c r="C101" s="66">
         <f t="shared" si="5"/>
-        <v>0.42255999999999999</v>
-      </c>
-      <c r="C101" s="66">
+        <v>0.41797000000000001</v>
+      </c>
+      <c r="D101" s="66">
         <f t="shared" si="6"/>
-        <v>0.41797000000000001</v>
-      </c>
-      <c r="D101" s="66">
+        <v>0.44034200000000001</v>
+      </c>
+      <c r="E101" s="59">
         <f t="shared" si="7"/>
-        <v>0.44034200000000001</v>
-      </c>
-      <c r="E101" s="59">
-        <f t="shared" si="8"/>
         <v>0.42695733333333336</v>
       </c>
       <c r="F101" s="59">
@@ -17809,24 +17809,24 @@
         <v>151</v>
       </c>
     </row>
-    <row r="102" spans="1:17" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:17" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="64">
         <v>520</v>
       </c>
       <c r="B102" s="66">
+        <f t="shared" si="8"/>
+        <v>0.42070999999999997</v>
+      </c>
+      <c r="C102" s="66">
         <f t="shared" si="5"/>
-        <v>0.42070999999999997</v>
-      </c>
-      <c r="C102" s="66">
+        <v>0.41469999999999996</v>
+      </c>
+      <c r="D102" s="66">
         <f t="shared" si="6"/>
-        <v>0.41469999999999996</v>
-      </c>
-      <c r="D102" s="66">
+        <v>0.43669000000000002</v>
+      </c>
+      <c r="E102" s="59">
         <f t="shared" si="7"/>
-        <v>0.43669000000000002</v>
-      </c>
-      <c r="E102" s="59">
-        <f t="shared" si="8"/>
         <v>0.42403333333333332</v>
       </c>
       <c r="F102" s="59">
@@ -17867,24 +17867,24 @@
         <v>152</v>
       </c>
     </row>
-    <row r="103" spans="1:17" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:17" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="64">
         <v>515</v>
       </c>
       <c r="B103" s="66">
+        <f t="shared" si="8"/>
+        <v>0.4140766666666667</v>
+      </c>
+      <c r="C103" s="66">
         <f t="shared" si="5"/>
-        <v>0.4140766666666667</v>
-      </c>
-      <c r="C103" s="66">
+        <v>0.40622249999999999</v>
+      </c>
+      <c r="D103" s="66">
         <f t="shared" si="6"/>
-        <v>0.40622249999999999</v>
-      </c>
-      <c r="D103" s="66">
+        <v>0.42727399999999999</v>
+      </c>
+      <c r="E103" s="59">
         <f t="shared" si="7"/>
-        <v>0.42727399999999999</v>
-      </c>
-      <c r="E103" s="59">
-        <f t="shared" si="8"/>
         <v>0.41585772222222223</v>
       </c>
       <c r="F103" s="59">
@@ -17925,24 +17925,24 @@
         <v>153</v>
       </c>
     </row>
-    <row r="104" spans="1:17" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:17" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="64">
         <v>510</v>
       </c>
       <c r="B104" s="66">
+        <f t="shared" si="8"/>
+        <v>0.40134999999999998</v>
+      </c>
+      <c r="C104" s="66">
         <f t="shared" si="5"/>
-        <v>0.40134999999999998</v>
-      </c>
-      <c r="C104" s="66">
+        <v>0.39217750000000001</v>
+      </c>
+      <c r="D104" s="66">
         <f t="shared" si="6"/>
-        <v>0.39217750000000001</v>
-      </c>
-      <c r="D104" s="66">
+        <v>0.41186400000000001</v>
+      </c>
+      <c r="E104" s="59">
         <f t="shared" si="7"/>
-        <v>0.41186400000000001</v>
-      </c>
-      <c r="E104" s="59">
-        <f t="shared" si="8"/>
         <v>0.40179716666666665</v>
       </c>
       <c r="F104" s="59">
@@ -17983,24 +17983,24 @@
         <v>154</v>
       </c>
     </row>
-    <row r="105" spans="1:17" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:17" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="64">
         <v>505</v>
       </c>
       <c r="B105" s="66">
+        <f t="shared" si="8"/>
+        <v>0.38486666666666663</v>
+      </c>
+      <c r="C105" s="66">
         <f t="shared" si="5"/>
-        <v>0.38486666666666663</v>
-      </c>
-      <c r="C105" s="66">
+        <v>0.37326749999999997</v>
+      </c>
+      <c r="D105" s="66">
         <f t="shared" si="6"/>
-        <v>0.37326749999999997</v>
-      </c>
-      <c r="D105" s="66">
+        <v>0.39184000000000002</v>
+      </c>
+      <c r="E105" s="59">
         <f t="shared" si="7"/>
-        <v>0.39184000000000002</v>
-      </c>
-      <c r="E105" s="59">
-        <f t="shared" si="8"/>
         <v>0.38332472222222219</v>
       </c>
       <c r="F105" s="59">
@@ -18041,24 +18041,24 @@
         <v>155</v>
       </c>
     </row>
-    <row r="106" spans="1:17" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:17" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="64">
         <v>500</v>
       </c>
       <c r="B106" s="66">
+        <f t="shared" si="8"/>
+        <v>0.36566333333333334</v>
+      </c>
+      <c r="C106" s="66">
         <f t="shared" si="5"/>
-        <v>0.36566333333333334</v>
-      </c>
-      <c r="C106" s="66">
+        <v>0.35205249999999999</v>
+      </c>
+      <c r="D106" s="66">
         <f t="shared" si="6"/>
-        <v>0.35205249999999999</v>
-      </c>
-      <c r="D106" s="66">
+        <v>0.368674</v>
+      </c>
+      <c r="E106" s="59">
         <f t="shared" si="7"/>
-        <v>0.368674</v>
-      </c>
-      <c r="E106" s="59">
-        <f t="shared" si="8"/>
         <v>0.36212994444444441</v>
       </c>
       <c r="F106" s="59">
@@ -18099,24 +18099,24 @@
         <v>156</v>
       </c>
     </row>
-    <row r="107" spans="1:17" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:17" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="64">
         <v>495</v>
       </c>
       <c r="B107" s="66">
+        <f t="shared" si="8"/>
+        <v>0.34465666666666667</v>
+      </c>
+      <c r="C107" s="66">
         <f t="shared" si="5"/>
-        <v>0.34465666666666667</v>
-      </c>
-      <c r="C107" s="66">
+        <v>0.32928999999999997</v>
+      </c>
+      <c r="D107" s="66">
         <f t="shared" si="6"/>
-        <v>0.32928999999999997</v>
-      </c>
-      <c r="D107" s="66">
+        <v>0.34410600000000002</v>
+      </c>
+      <c r="E107" s="59">
         <f t="shared" si="7"/>
-        <v>0.34410600000000002</v>
-      </c>
-      <c r="E107" s="59">
-        <f t="shared" si="8"/>
         <v>0.33935088888888892</v>
       </c>
       <c r="F107" s="59">
@@ -18157,24 +18157,24 @@
         <v>157</v>
       </c>
     </row>
-    <row r="108" spans="1:17" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:17" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="64">
         <v>490</v>
       </c>
       <c r="B108" s="66">
+        <f t="shared" si="8"/>
+        <v>0.32189033333333333</v>
+      </c>
+      <c r="C108" s="66">
         <f t="shared" si="5"/>
-        <v>0.32189033333333333</v>
-      </c>
-      <c r="C108" s="66">
+        <v>0.30483250000000001</v>
+      </c>
+      <c r="D108" s="66">
         <f t="shared" si="6"/>
-        <v>0.30483250000000001</v>
-      </c>
-      <c r="D108" s="66">
+        <v>0.31625999999999999</v>
+      </c>
+      <c r="E108" s="59">
         <f t="shared" si="7"/>
-        <v>0.31625999999999999</v>
-      </c>
-      <c r="E108" s="59">
-        <f t="shared" si="8"/>
         <v>0.31432761111111113</v>
       </c>
       <c r="F108" s="59">
@@ -18215,24 +18215,24 @@
         <v>158</v>
       </c>
     </row>
-    <row r="109" spans="1:17" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:17" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="64">
         <v>485</v>
       </c>
       <c r="B109" s="66">
+        <f t="shared" si="8"/>
+        <v>0.29691333333333336</v>
+      </c>
+      <c r="C109" s="66">
         <f t="shared" si="5"/>
-        <v>0.29691333333333336</v>
-      </c>
-      <c r="C109" s="66">
+        <v>0.27717499999999995</v>
+      </c>
+      <c r="D109" s="66">
         <f t="shared" si="6"/>
-        <v>0.27717499999999995</v>
-      </c>
-      <c r="D109" s="66">
+        <v>0.28625200000000001</v>
+      </c>
+      <c r="E109" s="59">
         <f t="shared" si="7"/>
-        <v>0.28625200000000001</v>
-      </c>
-      <c r="E109" s="59">
-        <f t="shared" si="8"/>
         <v>0.28678011111111107</v>
       </c>
       <c r="F109" s="59">
@@ -18273,20 +18273,20 @@
         <v>159</v>
       </c>
     </row>
-    <row r="110" spans="1:17" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:17" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A110" s="65">
         <v>480</v>
       </c>
       <c r="B110" s="66">
+        <f t="shared" si="8"/>
+        <v>0.269845</v>
+      </c>
+      <c r="C110" s="66">
         <f t="shared" si="5"/>
-        <v>0.269845</v>
-      </c>
-      <c r="C110" s="66">
+        <v>0.24775624999999998</v>
+      </c>
+      <c r="D110" s="66">
         <f t="shared" si="6"/>
-        <v>0.24775624999999998</v>
-      </c>
-      <c r="D110" s="66">
-        <f t="shared" si="7"/>
         <v>0.25325399999999998</v>
       </c>
       <c r="E110" s="59">
@@ -18331,7 +18331,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="111" spans="1:17" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:17" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B111" s="17"/>
       <c r="C111" s="17"/>
       <c r="D111" s="17"/>
@@ -18339,38 +18339,38 @@
         <v>161</v>
       </c>
     </row>
-    <row r="112" spans="1:17" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:17" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="B112" s="128" t="s">
+      <c r="B112" s="120" t="s">
         <v>100</v>
       </c>
-      <c r="C112" s="128"/>
-      <c r="D112" s="128"/>
-      <c r="E112" s="128"/>
-      <c r="F112" s="129"/>
-    </row>
-    <row r="113" spans="1:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C112" s="120"/>
+      <c r="D112" s="120"/>
+      <c r="E112" s="120"/>
+      <c r="F112" s="121"/>
+    </row>
+    <row r="113" spans="1:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="8"/>
-      <c r="B113" s="130"/>
-      <c r="C113" s="130"/>
-      <c r="D113" s="130"/>
-      <c r="E113" s="130"/>
-      <c r="F113" s="131"/>
-    </row>
-    <row r="114" spans="1:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B113" s="122"/>
+      <c r="C113" s="122"/>
+      <c r="D113" s="122"/>
+      <c r="E113" s="122"/>
+      <c r="F113" s="123"/>
+    </row>
+    <row r="114" spans="1:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="6"/>
     </row>
-    <row r="115" spans="1:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="6" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="116" spans="1:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="6"/>
     </row>
-    <row r="117" spans="1:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="62" t="s">
         <v>27</v>
       </c>
@@ -18396,7 +18396,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="118" spans="1:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" s="48">
         <v>550</v>
       </c>
@@ -18413,504 +18413,504 @@
         <v>0.22112399999999999</v>
       </c>
       <c r="E118" s="69">
-        <f t="shared" ref="E118:E132" si="11">J96</f>
+        <f>J96</f>
         <v>0.35936772222222224</v>
       </c>
       <c r="F118" s="69">
-        <f t="shared" ref="F118:F132" si="12">E96</f>
+        <f t="shared" ref="F118:F132" si="11">E96</f>
         <v>0.38005327777777781</v>
       </c>
       <c r="G118" s="69">
-        <f t="shared" ref="G118:G132" si="13">F118/E118</f>
+        <f t="shared" ref="G118:G132" si="12">F118/E118</f>
         <v>1.057560972442495</v>
       </c>
       <c r="H118" s="51">
-        <f t="shared" ref="H118:H132" si="14">D118/E118</f>
+        <f t="shared" ref="H118:H132" si="13">D118/E118</f>
         <v>0.61531402606955199</v>
       </c>
     </row>
-    <row r="119" spans="1:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" s="26">
         <v>545</v>
       </c>
       <c r="B119" s="59">
-        <f t="shared" ref="B119:B132" si="15">G119</f>
+        <f t="shared" ref="B119:B132" si="14">G119</f>
         <v>0.99636021489650051</v>
       </c>
       <c r="C119" s="40">
-        <f t="shared" ref="C119:C132" si="16">H119</f>
+        <f t="shared" ref="C119:C132" si="15">H119</f>
         <v>0.61608380796376228</v>
       </c>
       <c r="D119" s="35">
-        <f t="shared" ref="D119:D132" si="17">J54</f>
+        <f t="shared" ref="D119:D132" si="16">J54</f>
         <v>0.245724</v>
       </c>
       <c r="E119" s="69">
+        <f t="shared" ref="E118:E132" si="17">J97</f>
+        <v>0.39884833333333336</v>
+      </c>
+      <c r="F119" s="69">
         <f t="shared" si="11"/>
-        <v>0.39884833333333336</v>
-      </c>
-      <c r="F119" s="69">
+        <v>0.39739661111111108</v>
+      </c>
+      <c r="G119" s="69">
         <f t="shared" si="12"/>
-        <v>0.39739661111111108</v>
-      </c>
-      <c r="G119" s="69">
+        <v>0.99636021489650051</v>
+      </c>
+      <c r="H119" s="51">
         <f t="shared" si="13"/>
-        <v>0.99636021489650051</v>
-      </c>
-      <c r="H119" s="51">
-        <f t="shared" si="14"/>
         <v>0.61608380796376228</v>
       </c>
     </row>
-    <row r="120" spans="1:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" s="26">
         <v>540</v>
       </c>
       <c r="B120" s="59">
+        <f t="shared" si="14"/>
+        <v>0.89323126154716548</v>
+      </c>
+      <c r="C120" s="40">
         <f t="shared" si="15"/>
+        <v>0.5890230527348157</v>
+      </c>
+      <c r="D120" s="35">
+        <f t="shared" si="16"/>
+        <v>0.27023000000000003</v>
+      </c>
+      <c r="E120" s="69">
+        <f t="shared" si="17"/>
+        <v>0.45877661111111112</v>
+      </c>
+      <c r="F120" s="69">
+        <f t="shared" si="11"/>
+        <v>0.40979361111111112</v>
+      </c>
+      <c r="G120" s="69">
+        <f t="shared" si="12"/>
         <v>0.89323126154716548</v>
       </c>
-      <c r="C120" s="40">
-        <f t="shared" si="16"/>
+      <c r="H120" s="51">
+        <f t="shared" si="13"/>
         <v>0.5890230527348157</v>
       </c>
-      <c r="D120" s="35">
-        <f t="shared" si="17"/>
-        <v>0.27023000000000003</v>
-      </c>
-      <c r="E120" s="69">
-        <f t="shared" si="11"/>
-        <v>0.45877661111111112</v>
-      </c>
-      <c r="F120" s="69">
-        <f t="shared" si="12"/>
-        <v>0.40979361111111112</v>
-      </c>
-      <c r="G120" s="69">
-        <f t="shared" si="13"/>
-        <v>0.89323126154716548</v>
-      </c>
-      <c r="H120" s="51">
-        <f t="shared" si="14"/>
-        <v>0.5890230527348157</v>
-      </c>
-    </row>
-    <row r="121" spans="1:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="121" spans="1:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" s="26">
         <v>535</v>
       </c>
       <c r="B121" s="59">
+        <f t="shared" si="14"/>
+        <v>0.83503666787858366</v>
+      </c>
+      <c r="C121" s="40">
         <f t="shared" si="15"/>
+        <v>0.57923099433354919</v>
+      </c>
+      <c r="D121" s="35">
+        <f t="shared" si="16"/>
+        <v>0.29030800000000001</v>
+      </c>
+      <c r="E121" s="69">
+        <f t="shared" si="17"/>
+        <v>0.50119555555555551</v>
+      </c>
+      <c r="F121" s="69">
+        <f t="shared" si="11"/>
+        <v>0.41851666666666665</v>
+      </c>
+      <c r="G121" s="69">
+        <f t="shared" si="12"/>
         <v>0.83503666787858366</v>
       </c>
-      <c r="C121" s="40">
-        <f t="shared" si="16"/>
+      <c r="H121" s="51">
+        <f t="shared" si="13"/>
         <v>0.57923099433354919</v>
       </c>
-      <c r="D121" s="35">
-        <f t="shared" si="17"/>
-        <v>0.29030800000000001</v>
-      </c>
-      <c r="E121" s="69">
-        <f t="shared" si="11"/>
-        <v>0.50119555555555551</v>
-      </c>
-      <c r="F121" s="69">
-        <f t="shared" si="12"/>
-        <v>0.41851666666666665</v>
-      </c>
-      <c r="G121" s="69">
-        <f t="shared" si="13"/>
-        <v>0.83503666787858366</v>
-      </c>
-      <c r="H121" s="51">
-        <f t="shared" si="14"/>
-        <v>0.57923099433354919</v>
-      </c>
-    </row>
-    <row r="122" spans="1:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="122" spans="1:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" s="26">
         <v>530</v>
       </c>
       <c r="B122" s="59">
+        <f t="shared" si="14"/>
+        <v>0.80811054047247788</v>
+      </c>
+      <c r="C122" s="40">
         <f t="shared" si="15"/>
+        <v>0.5753628165605098</v>
+      </c>
+      <c r="D122" s="35">
+        <f t="shared" si="16"/>
+        <v>0.30221599999999998</v>
+      </c>
+      <c r="E122" s="69">
+        <f t="shared" si="17"/>
+        <v>0.52526161111111103</v>
+      </c>
+      <c r="F122" s="69">
+        <f t="shared" si="11"/>
+        <v>0.4244694444444444</v>
+      </c>
+      <c r="G122" s="69">
+        <f t="shared" si="12"/>
         <v>0.80811054047247788</v>
       </c>
-      <c r="C122" s="40">
-        <f t="shared" si="16"/>
+      <c r="H122" s="51">
+        <f t="shared" si="13"/>
         <v>0.5753628165605098</v>
       </c>
-      <c r="D122" s="35">
-        <f t="shared" si="17"/>
-        <v>0.30221599999999998</v>
-      </c>
-      <c r="E122" s="69">
-        <f t="shared" si="11"/>
-        <v>0.52526161111111103</v>
-      </c>
-      <c r="F122" s="69">
-        <f t="shared" si="12"/>
-        <v>0.4244694444444444</v>
-      </c>
-      <c r="G122" s="69">
-        <f t="shared" si="13"/>
-        <v>0.80811054047247788</v>
-      </c>
-      <c r="H122" s="51">
-        <f t="shared" si="14"/>
-        <v>0.5753628165605098</v>
-      </c>
-    </row>
-    <row r="123" spans="1:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="123" spans="1:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" s="26">
         <v>525</v>
       </c>
       <c r="B123" s="59">
+        <f t="shared" si="14"/>
+        <v>0.80330720529654587</v>
+      </c>
+      <c r="C123" s="40">
         <f t="shared" si="15"/>
+        <v>0.57585196597885013</v>
+      </c>
+      <c r="D123" s="35">
+        <f t="shared" si="16"/>
+        <v>0.30606499999999998</v>
+      </c>
+      <c r="E123" s="69">
+        <f t="shared" si="17"/>
+        <v>0.53149944444444441</v>
+      </c>
+      <c r="F123" s="69">
+        <f t="shared" si="11"/>
+        <v>0.42695733333333336</v>
+      </c>
+      <c r="G123" s="69">
+        <f t="shared" si="12"/>
         <v>0.80330720529654587</v>
       </c>
-      <c r="C123" s="40">
-        <f t="shared" si="16"/>
+      <c r="H123" s="51">
+        <f t="shared" si="13"/>
         <v>0.57585196597885013</v>
       </c>
-      <c r="D123" s="35">
-        <f t="shared" si="17"/>
-        <v>0.30606499999999998</v>
-      </c>
-      <c r="E123" s="69">
-        <f t="shared" si="11"/>
-        <v>0.53149944444444441</v>
-      </c>
-      <c r="F123" s="69">
-        <f t="shared" si="12"/>
-        <v>0.42695733333333336</v>
-      </c>
-      <c r="G123" s="69">
-        <f t="shared" si="13"/>
-        <v>0.80330720529654587</v>
-      </c>
-      <c r="H123" s="51">
-        <f t="shared" si="14"/>
-        <v>0.57585196597885013</v>
-      </c>
-    </row>
-    <row r="124" spans="1:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="124" spans="1:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" s="26">
         <v>520</v>
       </c>
       <c r="B124" s="59">
+        <f t="shared" si="14"/>
+        <v>0.79929669096029021</v>
+      </c>
+      <c r="C124" s="40">
         <f t="shared" si="15"/>
+        <v>0.5768451521052409</v>
+      </c>
+      <c r="D124" s="35">
+        <f t="shared" si="16"/>
+        <v>0.30602099999999999</v>
+      </c>
+      <c r="E124" s="69">
+        <f t="shared" si="17"/>
+        <v>0.53050805555555547</v>
+      </c>
+      <c r="F124" s="69">
+        <f t="shared" si="11"/>
+        <v>0.42403333333333332</v>
+      </c>
+      <c r="G124" s="69">
+        <f t="shared" si="12"/>
         <v>0.79929669096029021</v>
       </c>
-      <c r="C124" s="40">
-        <f t="shared" si="16"/>
+      <c r="H124" s="51">
+        <f t="shared" si="13"/>
         <v>0.5768451521052409</v>
       </c>
-      <c r="D124" s="35">
-        <f t="shared" si="17"/>
-        <v>0.30602099999999999</v>
-      </c>
-      <c r="E124" s="69">
-        <f t="shared" si="11"/>
-        <v>0.53050805555555547</v>
-      </c>
-      <c r="F124" s="69">
-        <f t="shared" si="12"/>
-        <v>0.42403333333333332</v>
-      </c>
-      <c r="G124" s="69">
-        <f t="shared" si="13"/>
-        <v>0.79929669096029021</v>
-      </c>
-      <c r="H124" s="51">
-        <f t="shared" si="14"/>
-        <v>0.5768451521052409</v>
-      </c>
-    </row>
-    <row r="125" spans="1:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="125" spans="1:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" s="26">
         <v>515</v>
       </c>
       <c r="B125" s="59">
+        <f t="shared" si="14"/>
+        <v>0.78189761951468573</v>
+      </c>
+      <c r="C125" s="40">
         <f t="shared" si="15"/>
+        <v>0.57500042304604426</v>
+      </c>
+      <c r="D125" s="35">
+        <f t="shared" si="16"/>
+        <v>0.30581799999999998</v>
+      </c>
+      <c r="E125" s="69">
+        <f t="shared" si="17"/>
+        <v>0.53185700000000002</v>
+      </c>
+      <c r="F125" s="69">
+        <f t="shared" si="11"/>
+        <v>0.41585772222222223</v>
+      </c>
+      <c r="G125" s="69">
+        <f t="shared" si="12"/>
         <v>0.78189761951468573</v>
       </c>
-      <c r="C125" s="40">
-        <f t="shared" si="16"/>
+      <c r="H125" s="51">
+        <f t="shared" si="13"/>
         <v>0.57500042304604426</v>
       </c>
-      <c r="D125" s="35">
-        <f t="shared" si="17"/>
-        <v>0.30581799999999998</v>
-      </c>
-      <c r="E125" s="69">
-        <f t="shared" si="11"/>
-        <v>0.53185700000000002</v>
-      </c>
-      <c r="F125" s="69">
-        <f t="shared" si="12"/>
-        <v>0.41585772222222223</v>
-      </c>
-      <c r="G125" s="69">
-        <f t="shared" si="13"/>
-        <v>0.78189761951468573</v>
-      </c>
-      <c r="H125" s="51">
-        <f t="shared" si="14"/>
-        <v>0.57500042304604426</v>
-      </c>
-    </row>
-    <row r="126" spans="1:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="126" spans="1:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" s="26">
         <v>510</v>
       </c>
       <c r="B126" s="59">
+        <f t="shared" si="14"/>
+        <v>0.75094499562194861</v>
+      </c>
+      <c r="C126" s="40">
         <f t="shared" si="15"/>
+        <v>0.5702718005207561</v>
+      </c>
+      <c r="D126" s="35">
+        <f t="shared" si="16"/>
+        <v>0.30512699999999998</v>
+      </c>
+      <c r="E126" s="69">
+        <f t="shared" si="17"/>
+        <v>0.53505538888888882</v>
+      </c>
+      <c r="F126" s="69">
+        <f t="shared" si="11"/>
+        <v>0.40179716666666665</v>
+      </c>
+      <c r="G126" s="69">
+        <f t="shared" si="12"/>
         <v>0.75094499562194861</v>
       </c>
-      <c r="C126" s="40">
-        <f t="shared" si="16"/>
+      <c r="H126" s="51">
+        <f t="shared" si="13"/>
         <v>0.5702718005207561</v>
       </c>
-      <c r="D126" s="35">
-        <f t="shared" si="17"/>
-        <v>0.30512699999999998</v>
-      </c>
-      <c r="E126" s="69">
-        <f t="shared" si="11"/>
-        <v>0.53505538888888882</v>
-      </c>
-      <c r="F126" s="69">
-        <f t="shared" si="12"/>
-        <v>0.40179716666666665</v>
-      </c>
-      <c r="G126" s="69">
-        <f t="shared" si="13"/>
-        <v>0.75094499562194861</v>
-      </c>
-      <c r="H126" s="51">
-        <f t="shared" si="14"/>
-        <v>0.5702718005207561</v>
-      </c>
-    </row>
-    <row r="127" spans="1:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="127" spans="1:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127" s="26">
         <v>505</v>
       </c>
       <c r="B127" s="59">
+        <f t="shared" si="14"/>
+        <v>0.71647419902875042</v>
+      </c>
+      <c r="C127" s="40">
         <f t="shared" si="15"/>
+        <v>0.56513514616453908</v>
+      </c>
+      <c r="D127" s="35">
+        <f t="shared" si="16"/>
+        <v>0.30235600000000001</v>
+      </c>
+      <c r="E127" s="69">
+        <f t="shared" si="17"/>
+        <v>0.535015388888889</v>
+      </c>
+      <c r="F127" s="69">
+        <f t="shared" si="11"/>
+        <v>0.38332472222222219</v>
+      </c>
+      <c r="G127" s="69">
+        <f t="shared" si="12"/>
         <v>0.71647419902875042</v>
       </c>
-      <c r="C127" s="40">
-        <f t="shared" si="16"/>
+      <c r="H127" s="51">
+        <f t="shared" si="13"/>
         <v>0.56513514616453908</v>
       </c>
-      <c r="D127" s="35">
-        <f t="shared" si="17"/>
-        <v>0.30235600000000001</v>
-      </c>
-      <c r="E127" s="69">
-        <f t="shared" si="11"/>
-        <v>0.535015388888889</v>
-      </c>
-      <c r="F127" s="69">
-        <f t="shared" si="12"/>
-        <v>0.38332472222222219</v>
-      </c>
-      <c r="G127" s="69">
-        <f t="shared" si="13"/>
-        <v>0.71647419902875042</v>
-      </c>
-      <c r="H127" s="51">
-        <f t="shared" si="14"/>
-        <v>0.56513514616453908</v>
-      </c>
-    </row>
-    <row r="128" spans="1:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="128" spans="1:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A128" s="26">
         <v>500</v>
       </c>
       <c r="B128" s="59">
+        <f t="shared" si="14"/>
+        <v>0.68759118574618894</v>
+      </c>
+      <c r="C128" s="40">
         <f t="shared" si="15"/>
+        <v>0.56083130282259541</v>
+      </c>
+      <c r="D128" s="35">
+        <f t="shared" si="16"/>
+        <v>0.29537000000000002</v>
+      </c>
+      <c r="E128" s="69">
+        <f t="shared" si="17"/>
+        <v>0.52666461111111118</v>
+      </c>
+      <c r="F128" s="69">
+        <f t="shared" si="11"/>
+        <v>0.36212994444444441</v>
+      </c>
+      <c r="G128" s="69">
+        <f t="shared" si="12"/>
         <v>0.68759118574618894</v>
       </c>
-      <c r="C128" s="40">
-        <f t="shared" si="16"/>
+      <c r="H128" s="51">
+        <f t="shared" si="13"/>
         <v>0.56083130282259541</v>
       </c>
-      <c r="D128" s="35">
-        <f t="shared" si="17"/>
-        <v>0.29537000000000002</v>
-      </c>
-      <c r="E128" s="69">
-        <f t="shared" si="11"/>
-        <v>0.52666461111111118</v>
-      </c>
-      <c r="F128" s="69">
-        <f t="shared" si="12"/>
-        <v>0.36212994444444441</v>
-      </c>
-      <c r="G128" s="69">
-        <f t="shared" si="13"/>
-        <v>0.68759118574618894</v>
-      </c>
-      <c r="H128" s="51">
-        <f t="shared" si="14"/>
-        <v>0.56083130282259541</v>
-      </c>
-    </row>
-    <row r="129" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="129" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129" s="26">
         <v>495</v>
       </c>
       <c r="B129" s="59">
+        <f t="shared" si="14"/>
+        <v>0.66959073109868805</v>
+      </c>
+      <c r="C129" s="40">
         <f t="shared" si="15"/>
+        <v>0.55958183218521496</v>
+      </c>
+      <c r="D129" s="35">
+        <f t="shared" si="16"/>
+        <v>0.28359800000000002</v>
+      </c>
+      <c r="E129" s="69">
+        <f t="shared" si="17"/>
+        <v>0.50680344444444447</v>
+      </c>
+      <c r="F129" s="69">
+        <f t="shared" si="11"/>
+        <v>0.33935088888888892</v>
+      </c>
+      <c r="G129" s="69">
+        <f t="shared" si="12"/>
         <v>0.66959073109868805</v>
       </c>
-      <c r="C129" s="40">
-        <f t="shared" si="16"/>
+      <c r="H129" s="51">
+        <f t="shared" si="13"/>
         <v>0.55958183218521496</v>
       </c>
-      <c r="D129" s="35">
-        <f t="shared" si="17"/>
-        <v>0.28359800000000002</v>
-      </c>
-      <c r="E129" s="69">
-        <f t="shared" si="11"/>
-        <v>0.50680344444444447</v>
-      </c>
-      <c r="F129" s="69">
-        <f t="shared" si="12"/>
-        <v>0.33935088888888892</v>
-      </c>
-      <c r="G129" s="69">
-        <f t="shared" si="13"/>
-        <v>0.66959073109868805</v>
-      </c>
-      <c r="H129" s="51">
-        <f t="shared" si="14"/>
-        <v>0.55958183218521496</v>
-      </c>
-    </row>
-    <row r="130" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="130" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" s="26">
         <v>490</v>
       </c>
       <c r="B130" s="59">
+        <f t="shared" si="14"/>
+        <v>0.66132350096400949</v>
+      </c>
+      <c r="C130" s="40">
         <f t="shared" si="15"/>
+        <v>0.56017995620317662</v>
+      </c>
+      <c r="D130" s="35">
+        <f t="shared" si="16"/>
+        <v>0.26625399999999999</v>
+      </c>
+      <c r="E130" s="69">
+        <f t="shared" si="17"/>
+        <v>0.47530083333333328</v>
+      </c>
+      <c r="F130" s="69">
+        <f t="shared" si="11"/>
+        <v>0.31432761111111113</v>
+      </c>
+      <c r="G130" s="69">
+        <f t="shared" si="12"/>
         <v>0.66132350096400949</v>
       </c>
-      <c r="C130" s="40">
-        <f t="shared" si="16"/>
+      <c r="H130" s="51">
+        <f t="shared" si="13"/>
         <v>0.56017995620317662</v>
       </c>
-      <c r="D130" s="35">
-        <f t="shared" si="17"/>
-        <v>0.26625399999999999</v>
-      </c>
-      <c r="E130" s="69">
-        <f t="shared" si="11"/>
-        <v>0.47530083333333328</v>
-      </c>
-      <c r="F130" s="69">
-        <f t="shared" si="12"/>
-        <v>0.31432761111111113</v>
-      </c>
-      <c r="G130" s="69">
-        <f t="shared" si="13"/>
-        <v>0.66132350096400949</v>
-      </c>
-      <c r="H130" s="51">
-        <f t="shared" si="14"/>
-        <v>0.56017995620317662</v>
-      </c>
-    </row>
-    <row r="131" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="131" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A131" s="26">
         <v>485</v>
       </c>
       <c r="B131" s="59">
+        <f t="shared" si="14"/>
+        <v>0.65673823596354297</v>
+      </c>
+      <c r="C131" s="40">
         <f t="shared" si="15"/>
+        <v>0.56180432845753892</v>
+      </c>
+      <c r="D131" s="35">
+        <f t="shared" si="16"/>
+        <v>0.24532499999999999</v>
+      </c>
+      <c r="E131" s="69">
+        <f t="shared" si="17"/>
+        <v>0.4366733888888889</v>
+      </c>
+      <c r="F131" s="69">
+        <f t="shared" si="11"/>
+        <v>0.28678011111111107</v>
+      </c>
+      <c r="G131" s="69">
+        <f t="shared" si="12"/>
         <v>0.65673823596354297</v>
       </c>
-      <c r="C131" s="40">
-        <f t="shared" si="16"/>
+      <c r="H131" s="51">
+        <f t="shared" si="13"/>
         <v>0.56180432845753892</v>
       </c>
-      <c r="D131" s="35">
-        <f t="shared" si="17"/>
-        <v>0.24532499999999999</v>
-      </c>
-      <c r="E131" s="69">
-        <f t="shared" si="11"/>
-        <v>0.4366733888888889</v>
-      </c>
-      <c r="F131" s="69">
-        <f t="shared" si="12"/>
-        <v>0.28678011111111107</v>
-      </c>
-      <c r="G131" s="69">
-        <f t="shared" si="13"/>
-        <v>0.65673823596354297</v>
-      </c>
-      <c r="H131" s="51">
-        <f t="shared" si="14"/>
-        <v>0.56180432845753892</v>
-      </c>
-    </row>
-    <row r="132" spans="1:9" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="132" spans="1:9" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A132" s="27">
         <v>480</v>
       </c>
       <c r="B132" s="59">
+        <f t="shared" si="14"/>
+        <v>0.64866202710025878</v>
+      </c>
+      <c r="C132" s="40">
         <f t="shared" si="15"/>
+        <v>0.56288687207093591</v>
+      </c>
+      <c r="D132" s="35">
+        <f t="shared" si="16"/>
+        <v>0.22297400000000001</v>
+      </c>
+      <c r="E132" s="69">
+        <f t="shared" si="17"/>
+        <v>0.3961257777777778</v>
+      </c>
+      <c r="F132" s="69">
+        <f t="shared" si="11"/>
+        <v>0.25695174999999998</v>
+      </c>
+      <c r="G132" s="69">
+        <f t="shared" si="12"/>
         <v>0.64866202710025878</v>
       </c>
-      <c r="C132" s="40">
-        <f t="shared" si="16"/>
+      <c r="H132" s="51">
+        <f t="shared" si="13"/>
         <v>0.56288687207093591</v>
       </c>
-      <c r="D132" s="35">
-        <f t="shared" si="17"/>
-        <v>0.22297400000000001</v>
-      </c>
-      <c r="E132" s="69">
-        <f t="shared" si="11"/>
-        <v>0.3961257777777778</v>
-      </c>
-      <c r="F132" s="69">
-        <f t="shared" si="12"/>
-        <v>0.25695174999999998</v>
-      </c>
-      <c r="G132" s="69">
-        <f t="shared" si="13"/>
-        <v>0.64866202710025878</v>
-      </c>
-      <c r="H132" s="51">
-        <f t="shared" si="14"/>
-        <v>0.56288687207093591</v>
-      </c>
-    </row>
-    <row r="133" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="133" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A133" s="6"/>
     </row>
-    <row r="135" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135" s="13"/>
       <c r="B135" s="14"/>
       <c r="C135" s="14"/>
       <c r="D135" s="15"/>
     </row>
-    <row r="136" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A136" s="9"/>
       <c r="D136" s="10"/>
-      <c r="F136" s="132" t="s">
+      <c r="F136" s="124" t="s">
         <v>78</v>
       </c>
-      <c r="G136" s="132"/>
-      <c r="H136" s="132"/>
-      <c r="I136" s="132"/>
-    </row>
-    <row r="137" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G136" s="124"/>
+      <c r="H136" s="124"/>
+      <c r="I136" s="124"/>
+    </row>
+    <row r="137" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="9"/>
       <c r="D137" s="10"/>
       <c r="F137" s="54" t="s">
@@ -18927,7 +18927,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="138" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" s="9"/>
       <c r="D138" s="10"/>
       <c r="F138" s="54" t="s">
@@ -18943,7 +18943,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="139" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A139" s="9"/>
       <c r="D139" s="10"/>
       <c r="F139" s="55" t="s">
@@ -18959,7 +18959,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="140" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A140" s="9"/>
       <c r="D140" s="10"/>
       <c r="F140" s="54" t="s">
@@ -18975,7 +18975,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="141" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A141" s="9"/>
       <c r="D141" s="10"/>
       <c r="F141" s="54" t="s">
@@ -18991,7 +18991,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="142" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A142" s="9"/>
       <c r="D142" s="10"/>
       <c r="F142" s="20"/>
@@ -18999,7 +18999,7 @@
       <c r="H142" s="20"/>
       <c r="I142" s="20"/>
     </row>
-    <row r="143" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A143" s="9"/>
       <c r="D143" s="10"/>
       <c r="F143" s="16" t="s">
@@ -19012,7 +19012,7 @@
       <c r="H143" s="20"/>
       <c r="I143" s="20"/>
     </row>
-    <row r="144" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A144" s="9"/>
       <c r="D144" s="10"/>
       <c r="F144" s="16" t="s">
@@ -19025,7 +19025,7 @@
       <c r="H144" s="20"/>
       <c r="I144" s="20"/>
     </row>
-    <row r="145" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A145" s="9"/>
       <c r="D145" s="10"/>
       <c r="F145" s="16"/>
@@ -19033,7 +19033,7 @@
       <c r="H145" s="20"/>
       <c r="I145" s="20"/>
     </row>
-    <row r="146" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A146" s="8"/>
       <c r="B146" s="11"/>
       <c r="C146" s="11"/>
@@ -19042,7 +19042,7 @@
       <c r="H146" s="20"/>
       <c r="I146" s="20"/>
     </row>
-    <row r="147" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A147" s="7" t="s">
         <v>5</v>
       </c>
@@ -19051,7 +19051,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="148" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A148" s="7" t="s">
         <v>46</v>
       </c>
@@ -19067,7 +19067,7 @@
         <v>8.6401396390018669E-3</v>
       </c>
     </row>
-    <row r="149" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A149" s="7" t="s">
         <v>47</v>
       </c>
@@ -19083,30 +19083,30 @@
         <v>6.8552506351852891E-3</v>
       </c>
     </row>
-    <row r="151" spans="1:9" s="20" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:9" s="20" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A151" s="16" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="152" spans="1:9" s="20" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A152" s="126" t="s">
+    <row r="152" spans="1:9" s="20" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A152" s="115" t="s">
         <v>129</v>
       </c>
-      <c r="B152" s="126"/>
-      <c r="C152" s="126"/>
-      <c r="D152" s="126"/>
-      <c r="E152" s="126"/>
-      <c r="F152" s="126"/>
-    </row>
-    <row r="154" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B152" s="115"/>
+      <c r="C152" s="115"/>
+      <c r="D152" s="115"/>
+      <c r="E152" s="115"/>
+      <c r="F152" s="115"/>
+    </row>
+    <row r="154" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A154" s="6" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="155" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A155" s="6"/>
     </row>
-    <row r="156" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A156" s="7" t="s">
         <v>27</v>
       </c>
@@ -19132,7 +19132,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="157" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157" s="48">
         <v>550</v>
       </c>
@@ -19165,7 +19165,7 @@
         <v>0.82695796428882262</v>
       </c>
     </row>
-    <row r="158" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158" s="26">
         <v>545</v>
       </c>
@@ -19198,7 +19198,7 @@
         <v>0.81761404711063934</v>
       </c>
     </row>
-    <row r="159" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A159" s="26">
         <v>540</v>
       </c>
@@ -19231,7 +19231,7 @@
         <v>0.77137759735160372</v>
       </c>
     </row>
-    <row r="160" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A160" s="26">
         <v>535</v>
       </c>
@@ -19264,7 +19264,7 @@
         <v>0.75111400296180697</v>
       </c>
     </row>
-    <row r="161" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A161" s="26">
         <v>530</v>
       </c>
@@ -19297,7 +19297,7 @@
         <v>0.74270990254697433</v>
       </c>
     </row>
-    <row r="162" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A162" s="26">
         <v>525</v>
       </c>
@@ -19330,7 +19330,7 @@
         <v>0.74265552697347859</v>
       </c>
     </row>
-    <row r="163" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A163" s="26">
         <v>520</v>
       </c>
@@ -19363,7 +19363,7 @@
         <v>0.74358154578237123</v>
       </c>
     </row>
-    <row r="164" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A164" s="26">
         <v>515</v>
       </c>
@@ -19396,7 +19396,7 @@
         <v>0.73814765999131349</v>
       </c>
     </row>
-    <row r="165" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A165" s="26">
         <v>510</v>
       </c>
@@ -19429,7 +19429,7 @@
         <v>0.72745552718996809</v>
       </c>
     </row>
-    <row r="166" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A166" s="26">
         <v>505</v>
       </c>
@@ -19462,7 +19462,7 @@
         <v>0.71490466992797808</v>
       </c>
     </row>
-    <row r="167" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A167" s="26">
         <v>500</v>
       </c>
@@ -19495,7 +19495,7 @@
         <v>0.70437806561059357</v>
       </c>
     </row>
-    <row r="168" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A168" s="26">
         <v>495</v>
       </c>
@@ -19528,7 +19528,7 @@
         <v>0.69851932515586246</v>
       </c>
     </row>
-    <row r="169" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A169" s="26">
         <v>490</v>
       </c>
@@ -19561,7 +19561,7 @@
         <v>0.69583930177554221</v>
       </c>
     </row>
-    <row r="170" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A170" s="26">
         <v>485</v>
       </c>
@@ -19594,7 +19594,7 @@
         <v>0.69361680310010487</v>
       </c>
     </row>
-    <row r="171" spans="1:9" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:9" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A171" s="27">
         <v>480</v>
       </c>
@@ -19627,26 +19627,26 @@
         <v>0.68858937060394954</v>
       </c>
     </row>
-    <row r="172" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A172" s="6"/>
     </row>
-    <row r="174" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A174" s="13"/>
       <c r="B174" s="14"/>
       <c r="C174" s="14"/>
       <c r="D174" s="15"/>
     </row>
-    <row r="175" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A175" s="9"/>
       <c r="D175" s="10"/>
-      <c r="F175" s="132" t="s">
+      <c r="F175" s="124" t="s">
         <v>78</v>
       </c>
-      <c r="G175" s="132"/>
-      <c r="H175" s="132"/>
-      <c r="I175" s="132"/>
-    </row>
-    <row r="176" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G175" s="124"/>
+      <c r="H175" s="124"/>
+      <c r="I175" s="124"/>
+    </row>
+    <row r="176" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A176" s="9"/>
       <c r="D176" s="10"/>
       <c r="F176" s="54" t="s">
@@ -19663,7 +19663,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="177" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A177" s="9"/>
       <c r="D177" s="10"/>
       <c r="F177" s="54" t="s">
@@ -19679,7 +19679,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="178" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A178" s="9"/>
       <c r="D178" s="10"/>
       <c r="F178" s="55" t="s">
@@ -19695,7 +19695,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="179" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A179" s="9"/>
       <c r="D179" s="10"/>
       <c r="F179" s="54" t="s">
@@ -19711,7 +19711,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="180" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A180" s="9"/>
       <c r="D180" s="10"/>
       <c r="F180" s="54" t="s">
@@ -19727,7 +19727,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="181" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A181" s="9"/>
       <c r="D181" s="10"/>
       <c r="F181" s="20"/>
@@ -19735,7 +19735,7 @@
       <c r="H181" s="20"/>
       <c r="I181" s="20"/>
     </row>
-    <row r="182" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A182" s="9"/>
       <c r="D182" s="10"/>
       <c r="F182" s="16" t="s">
@@ -19748,7 +19748,7 @@
       <c r="H182" s="20"/>
       <c r="I182" s="20"/>
     </row>
-    <row r="183" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A183" s="9"/>
       <c r="D183" s="10"/>
       <c r="F183" s="16" t="s">
@@ -19761,17 +19761,17 @@
       <c r="H183" s="20"/>
       <c r="I183" s="20"/>
     </row>
-    <row r="184" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A184" s="9"/>
       <c r="D184" s="10"/>
     </row>
-    <row r="185" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A185" s="8"/>
       <c r="B185" s="11"/>
       <c r="C185" s="11"/>
       <c r="D185" s="12"/>
     </row>
-    <row r="186" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A186" s="7" t="s">
         <v>5</v>
       </c>
@@ -19780,7 +19780,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="187" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A187" s="7" t="s">
         <v>46</v>
       </c>
@@ -19796,7 +19796,7 @@
         <v>6.5565325931647486E-3</v>
       </c>
     </row>
-    <row r="188" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A188" s="7" t="s">
         <v>47</v>
       </c>
@@ -19812,30 +19812,30 @@
         <v>5.2020772929426929E-3</v>
       </c>
     </row>
-    <row r="190" spans="1:9" s="20" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:9" s="20" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A190" s="16" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="191" spans="1:9" s="20" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A191" s="127" t="s">
+    <row r="191" spans="1:9" s="20" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A191" s="119" t="s">
         <v>116</v>
       </c>
-      <c r="B191" s="127"/>
-      <c r="C191" s="127"/>
-      <c r="D191" s="127"/>
-      <c r="E191" s="127"/>
-      <c r="F191" s="127"/>
-    </row>
-    <row r="193" spans="1:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B191" s="119"/>
+      <c r="C191" s="119"/>
+      <c r="D191" s="119"/>
+      <c r="E191" s="119"/>
+      <c r="F191" s="119"/>
+    </row>
+    <row r="193" spans="1:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A193" s="6" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="194" spans="1:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A194" s="6"/>
     </row>
-    <row r="195" spans="1:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A195" s="7" t="s">
         <v>27</v>
       </c>
@@ -19861,7 +19861,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="196" spans="1:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A196" s="48">
         <v>550</v>
       </c>
@@ -19894,7 +19894,7 @@
         <v>0.62541788285876787</v>
       </c>
     </row>
-    <row r="197" spans="1:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A197" s="26">
         <v>545</v>
       </c>
@@ -19927,7 +19927,7 @@
         <v>0.60676447605397199</v>
       </c>
     </row>
-    <row r="198" spans="1:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A198" s="26">
         <v>540</v>
       </c>
@@ -19960,7 +19960,7 @@
         <v>0.56144318119481773</v>
       </c>
     </row>
-    <row r="199" spans="1:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A199" s="26">
         <v>535</v>
       </c>
@@ -19993,7 +19993,7 @@
         <v>0.53887748406033587</v>
       </c>
     </row>
-    <row r="200" spans="1:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A200" s="26">
         <v>530</v>
       </c>
@@ -20026,7 +20026,7 @@
         <v>0.52859183714697089</v>
       </c>
     </row>
-    <row r="201" spans="1:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A201" s="26">
         <v>525</v>
       </c>
@@ -20059,7 +20059,7 @@
         <v>0.52713131298349847</v>
       </c>
     </row>
-    <row r="202" spans="1:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A202" s="26">
         <v>520</v>
       </c>
@@ -20092,7 +20092,7 @@
         <v>0.52621067121716136</v>
       </c>
     </row>
-    <row r="203" spans="1:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A203" s="26">
         <v>515</v>
       </c>
@@ -20125,7 +20125,7 @@
         <v>0.51916210560357379</v>
       </c>
     </row>
-    <row r="204" spans="1:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A204" s="26">
         <v>510</v>
       </c>
@@ -20158,7 +20158,7 @@
         <v>0.50670828783354416</v>
       </c>
     </row>
-    <row r="205" spans="1:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A205" s="26">
         <v>505</v>
       </c>
@@ -20191,7 +20191,7 @@
         <v>0.49266620264401517</v>
       </c>
     </row>
-    <row r="206" spans="1:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A206" s="26">
         <v>500</v>
       </c>
@@ -20224,7 +20224,7 @@
         <v>0.48095883918534271</v>
       </c>
     </row>
-    <row r="207" spans="1:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A207" s="26">
         <v>495</v>
       </c>
@@ -20257,7 +20257,7 @@
         <v>0.47411477296370208</v>
       </c>
     </row>
-    <row r="208" spans="1:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A208" s="26">
         <v>490</v>
       </c>
@@ -20290,7 +20290,7 @@
         <v>0.47042837781685637</v>
       </c>
     </row>
-    <row r="209" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A209" s="26">
         <v>485</v>
       </c>
@@ -20323,7 +20323,7 @@
         <v>0.4690828550858186</v>
       </c>
     </row>
-    <row r="210" spans="1:9" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:9" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A210" s="27">
         <v>480</v>
       </c>
@@ -20356,27 +20356,27 @@
         <v>0.46525121650474649</v>
       </c>
     </row>
-    <row r="211" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A211" s="6"/>
       <c r="D211" s="29"/>
     </row>
-    <row r="213" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A213" s="13"/>
       <c r="B213" s="14"/>
       <c r="C213" s="14"/>
       <c r="D213" s="15"/>
     </row>
-    <row r="214" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A214" s="9"/>
       <c r="D214" s="10"/>
-      <c r="F214" s="132" t="s">
+      <c r="F214" s="124" t="s">
         <v>78</v>
       </c>
-      <c r="G214" s="132"/>
-      <c r="H214" s="132"/>
-      <c r="I214" s="132"/>
-    </row>
-    <row r="215" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G214" s="124"/>
+      <c r="H214" s="124"/>
+      <c r="I214" s="124"/>
+    </row>
+    <row r="215" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A215" s="9"/>
       <c r="D215" s="10"/>
       <c r="F215" s="54" t="s">
@@ -20393,7 +20393,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="216" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A216" s="9"/>
       <c r="D216" s="10"/>
       <c r="F216" s="54" t="s">
@@ -20409,7 +20409,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="217" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A217" s="9"/>
       <c r="D217" s="10"/>
       <c r="F217" s="55" t="s">
@@ -20425,7 +20425,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="218" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A218" s="9"/>
       <c r="D218" s="10"/>
       <c r="F218" s="54" t="s">
@@ -20441,7 +20441,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="219" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A219" s="9"/>
       <c r="D219" s="10"/>
       <c r="F219" s="54" t="s">
@@ -20457,7 +20457,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="220" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A220" s="9"/>
       <c r="D220" s="10"/>
       <c r="F220" s="20"/>
@@ -20465,7 +20465,7 @@
       <c r="H220" s="20"/>
       <c r="I220" s="20"/>
     </row>
-    <row r="221" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A221" s="9"/>
       <c r="D221" s="10"/>
       <c r="F221" s="16" t="s">
@@ -20478,7 +20478,7 @@
       <c r="H221" s="20"/>
       <c r="I221" s="20"/>
     </row>
-    <row r="222" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A222" s="9"/>
       <c r="D222" s="10"/>
       <c r="F222" s="16" t="s">
@@ -20491,17 +20491,17 @@
       <c r="H222" s="20"/>
       <c r="I222" s="20"/>
     </row>
-    <row r="223" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A223" s="9"/>
       <c r="D223" s="10"/>
     </row>
-    <row r="224" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A224" s="8"/>
       <c r="B224" s="11"/>
       <c r="C224" s="11"/>
       <c r="D224" s="12"/>
     </row>
-    <row r="225" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A225" s="7" t="s">
         <v>5</v>
       </c>
@@ -20510,7 +20510,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="226" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A226" s="7" t="s">
         <v>46</v>
       </c>
@@ -20526,7 +20526,7 @@
         <v>2.6703892887695721E-3</v>
       </c>
     </row>
-    <row r="227" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A227" s="7" t="s">
         <v>47</v>
       </c>
@@ -20542,29 +20542,29 @@
         <v>2.1187375011157091E-3</v>
       </c>
     </row>
-    <row r="229" spans="1:6" s="20" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:6" s="20" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A229" s="16" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="230" spans="1:6" s="20" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A230" s="127" t="s">
+    <row r="230" spans="1:6" s="20" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A230" s="119" t="s">
         <v>115</v>
       </c>
-      <c r="B230" s="127"/>
-      <c r="C230" s="127"/>
-      <c r="D230" s="127"/>
-      <c r="E230" s="127"/>
-      <c r="F230" s="127"/>
-    </row>
-    <row r="231" spans="1:6" ht="408" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="232" spans="1:6" ht="142.94999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B230" s="119"/>
+      <c r="C230" s="119"/>
+      <c r="D230" s="119"/>
+      <c r="E230" s="119"/>
+      <c r="F230" s="119"/>
+    </row>
+    <row r="231" spans="1:6" ht="408" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="232" spans="1:6" ht="143" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A232" s="16" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="233" spans="1:6" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="234" spans="1:6" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:6" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="234" spans="1:6" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A234" s="21" t="s">
         <v>54</v>
       </c>
@@ -20578,7 +20578,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="235" spans="1:6" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:6" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A235" s="21" t="s">
         <v>20</v>
       </c>
@@ -20589,7 +20589,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="236" spans="1:6" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:6" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A236" s="22" t="s">
         <v>21</v>
       </c>
@@ -20600,7 +20600,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="237" spans="1:6" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:6" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A237" s="23" t="s">
         <v>22</v>
       </c>
@@ -20613,42 +20613,42 @@
       <c r="E237" s="83"/>
       <c r="F237" s="83"/>
     </row>
-    <row r="238" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A238" s="17"/>
       <c r="B238" s="17"/>
     </row>
-    <row r="239" spans="1:6" s="20" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:6" s="20" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A239" s="16" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="240" spans="1:6" s="20" customFormat="1" ht="86.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A240" s="126" t="s">
+    <row r="240" spans="1:6" s="20" customFormat="1" ht="86.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A240" s="115" t="s">
         <v>130</v>
       </c>
-      <c r="B240" s="126"/>
-      <c r="C240" s="126"/>
-      <c r="D240" s="126"/>
-      <c r="E240" s="126"/>
-      <c r="F240" s="126"/>
-    </row>
-    <row r="242" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B240" s="115"/>
+      <c r="C240" s="115"/>
+      <c r="D240" s="115"/>
+      <c r="E240" s="115"/>
+      <c r="F240" s="115"/>
+    </row>
+    <row r="242" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A242" s="6" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="244" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A244" s="6" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="245" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A245" s="2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="246" spans="1:6" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="247" spans="1:6" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:6" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="247" spans="1:6" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A247" s="75" t="s">
         <v>54</v>
       </c>
@@ -20662,7 +20662,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="248" spans="1:6" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:6" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A248" s="75" t="s">
         <v>20</v>
       </c>
@@ -20681,7 +20681,7 @@
       <c r="E248"/>
       <c r="F248"/>
     </row>
-    <row r="249" spans="1:6" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:6" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A249" s="76" t="s">
         <v>21</v>
       </c>
@@ -20700,7 +20700,7 @@
       <c r="E249"/>
       <c r="F249" s="73"/>
     </row>
-    <row r="250" spans="1:6" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:6" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A250" s="77" t="s">
         <v>22</v>
       </c>
@@ -20714,47 +20714,47 @@
       </c>
       <c r="D250" s="90">
         <f>Solver!$I$5</f>
-        <v>1.120222250105557E-2</v>
+        <v>1.1202222501055599E-2</v>
       </c>
       <c r="E250"/>
       <c r="F250"/>
     </row>
-    <row r="251" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A251" s="24"/>
       <c r="B251" s="17"/>
     </row>
-    <row r="252" spans="1:6" s="20" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:6" s="20" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A252" s="16" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="253" spans="1:6" s="20" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A253" s="126" t="s">
+    <row r="253" spans="1:6" s="20" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A253" s="115" t="s">
         <v>142</v>
       </c>
-      <c r="B253" s="126"/>
-      <c r="C253" s="126"/>
-      <c r="D253" s="126"/>
-      <c r="E253" s="126"/>
-      <c r="F253" s="126"/>
-    </row>
-    <row r="255" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B253" s="115"/>
+      <c r="C253" s="115"/>
+      <c r="D253" s="115"/>
+      <c r="E253" s="115"/>
+      <c r="F253" s="115"/>
+    </row>
+    <row r="255" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A255" s="6" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="256" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A256" s="2" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="257" spans="1:6" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="258" spans="1:6" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:6" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="258" spans="1:6" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A258" s="21" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="259" spans="1:6" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:6" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A259" s="21" t="s">
         <v>20</v>
       </c>
@@ -20762,7 +20762,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="260" spans="1:6" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:6" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A260" s="22" t="s">
         <v>21</v>
       </c>
@@ -20770,7 +20770,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="261" spans="1:6" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:6" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A261" s="23" t="s">
         <v>22</v>
       </c>
@@ -20778,42 +20778,47 @@
         <v>164</v>
       </c>
     </row>
-    <row r="262" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A262" s="24"/>
       <c r="B262" s="17"/>
     </row>
-    <row r="263" spans="1:6" s="20" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:6" s="20" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A263" s="16" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="264" spans="1:6" s="20" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A264" s="126" t="s">
+    <row r="264" spans="1:6" s="20" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A264" s="115" t="s">
         <v>141</v>
       </c>
-      <c r="B264" s="126"/>
-      <c r="C264" s="126"/>
-      <c r="D264" s="126"/>
-      <c r="E264" s="126"/>
-      <c r="F264" s="126"/>
-    </row>
-    <row r="266" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B264" s="115"/>
+      <c r="C264" s="115"/>
+      <c r="D264" s="115"/>
+      <c r="E264" s="115"/>
+      <c r="F264" s="115"/>
+    </row>
+    <row r="266" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A266" s="6" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="267" spans="1:6" ht="114" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A267" s="126" t="s">
+    <row r="267" spans="1:6" ht="114" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A267" s="115" t="s">
         <v>143</v>
       </c>
-      <c r="B267" s="126"/>
-      <c r="C267" s="126"/>
-      <c r="D267" s="126"/>
-      <c r="E267" s="126"/>
-      <c r="F267" s="126"/>
+      <c r="B267" s="115"/>
+      <c r="C267" s="115"/>
+      <c r="D267" s="115"/>
+      <c r="E267" s="115"/>
+      <c r="F267" s="115"/>
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A6:D8"/>
+    <mergeCell ref="A10:D15"/>
+    <mergeCell ref="B85:F86"/>
+    <mergeCell ref="H51:J51"/>
+    <mergeCell ref="B17:D18"/>
     <mergeCell ref="A264:F264"/>
     <mergeCell ref="A267:F267"/>
     <mergeCell ref="A240:F240"/>
@@ -20827,11 +20832,6 @@
     <mergeCell ref="F136:I136"/>
     <mergeCell ref="F175:I175"/>
     <mergeCell ref="F214:I214"/>
-    <mergeCell ref="A6:D8"/>
-    <mergeCell ref="A10:D15"/>
-    <mergeCell ref="B85:F86"/>
-    <mergeCell ref="H51:J51"/>
-    <mergeCell ref="B17:D18"/>
   </mergeCells>
   <phoneticPr fontId="16" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -20843,15 +20843,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1400871-1C37-4265-810E-3A941BEA652D}">
   <dimension ref="A2:N65"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="19.33203125" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="4" max="4" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="9" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>93</v>
       </c>
@@ -20862,18 +20865,15 @@
         <v>64</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A3" s="61" t="s">
         <v>44</v>
       </c>
       <c r="B3" s="61" t="s">
         <v>44</v>
       </c>
-      <c r="G3" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A4" s="84">
         <f>'Pràctica A'!E118</f>
         <v>0.35936772222222224</v>
@@ -20913,7 +20913,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="84">
         <f>'Pràctica A'!E119</f>
         <v>0.39884833333333336</v>
@@ -20931,7 +20931,7 @@
       </c>
       <c r="F5" s="35">
         <f>A4*$G$5 + B4*$H$5 +$I$5</f>
-        <v>0.2226919573709486</v>
+        <v>0.22269195737094863</v>
       </c>
       <c r="G5">
         <v>0.44977360319330201</v>
@@ -20940,22 +20940,22 @@
         <v>0.13118060674584078</v>
       </c>
       <c r="I5">
-        <v>1.120222250105557E-2</v>
+        <v>1.1202222501055599E-2</v>
       </c>
       <c r="J5" s="86">
         <f>D5-F5</f>
-        <v>-1.5679573709486139E-3</v>
+        <v>-1.5679573709486416E-3</v>
       </c>
       <c r="K5" s="86">
         <f>J5^2</f>
-        <v>2.4584903171120893E-6</v>
+        <v>2.4584903171121761E-6</v>
       </c>
       <c r="L5" s="86">
         <f>SUM(K5:K19)</f>
-        <v>1.6487392254673265E-5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+        <v>1.6487392254673343E-5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A6" s="84">
         <f>'Pràctica A'!E120</f>
         <v>0.45877661111111112</v>
@@ -20973,18 +20973,18 @@
       </c>
       <c r="F6" s="35">
         <f t="shared" ref="F6:F19" si="0">A5*$G$5 + B5*$H$5 +$I$5</f>
-        <v>0.24272440307632859</v>
+        <v>0.24272440307632862</v>
       </c>
       <c r="J6" s="86">
         <f t="shared" ref="J6:J19" si="1">D6-F6</f>
-        <v>2.9995969236714104E-3</v>
+        <v>2.9995969236713826E-3</v>
       </c>
       <c r="K6" s="86">
         <f>J6^2</f>
-        <v>8.9975817044989894E-6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+        <v>8.9975817044988234E-6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A7" s="84">
         <f>'Pràctica A'!E121</f>
         <v>0.50119555555555551</v>
@@ -21002,18 +21002,18 @@
       </c>
       <c r="F7" s="35">
         <f t="shared" si="0"/>
-        <v>0.27130480648743699</v>
+        <v>0.27130480648743704</v>
       </c>
       <c r="J7" s="86">
         <f t="shared" si="1"/>
-        <v>-1.0748064874369634E-3</v>
+        <v>-1.0748064874370189E-3</v>
       </c>
       <c r="K7" s="86">
-        <f t="shared" ref="K6:K19" si="2">J7^2</f>
-        <v>1.1552089854365833E-6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+        <f t="shared" ref="K7:K19" si="2">J7^2</f>
+        <v>1.1552089854367027E-6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A8" s="84">
         <f>'Pràctica A'!E122</f>
         <v>0.52526161111111103</v>
@@ -21031,18 +21031,18 @@
       </c>
       <c r="F8" s="35">
         <f t="shared" si="0"/>
-        <v>0.29152802369432668</v>
+        <v>0.29152802369432673</v>
       </c>
       <c r="J8" s="86">
         <f t="shared" si="1"/>
-        <v>-1.2200236943266662E-3</v>
+        <v>-1.2200236943267218E-3</v>
       </c>
       <c r="K8" s="86">
         <f t="shared" si="2"/>
-        <v>1.4884578147184867E-6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+        <v>1.4884578147186222E-6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A9" s="84">
         <f>'Pràctica A'!E123</f>
         <v>0.53149944444444441</v>
@@ -21060,18 +21060,18 @@
       </c>
       <c r="F9" s="35">
         <f t="shared" si="0"/>
-        <v>0.30313318921691107</v>
+        <v>0.30313318921691113</v>
       </c>
       <c r="J9" s="86">
         <f t="shared" si="1"/>
-        <v>-9.1718921691108513E-4</v>
+        <v>-9.1718921691114064E-4</v>
       </c>
       <c r="K9" s="86">
         <f t="shared" si="2"/>
-        <v>8.4123605961796954E-7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+        <v>8.412360596180714E-7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A10" s="84">
         <f>'Pràctica A'!E124</f>
         <v>0.53050805555555547</v>
@@ -21089,18 +21089,18 @@
       </c>
       <c r="F10" s="35">
         <f t="shared" si="0"/>
-        <v>0.30626516476532445</v>
+        <v>0.3062651647653245</v>
       </c>
       <c r="J10" s="86">
         <f t="shared" si="1"/>
-        <v>-2.0016476532447314E-4</v>
+        <v>-2.0016476532452865E-4</v>
       </c>
       <c r="K10" s="86">
         <f t="shared" si="2"/>
-        <v>4.0065933277401402E-8</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+        <v>4.0065933277423624E-8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A11" s="84">
         <f>'Pràctica A'!E125</f>
         <v>0.53185700000000002</v>
@@ -21118,18 +21118,18 @@
       </c>
       <c r="F11" s="35">
         <f t="shared" si="0"/>
-        <v>0.30543569211847821</v>
+        <v>0.30543569211847826</v>
       </c>
       <c r="J11" s="86">
         <f t="shared" si="1"/>
-        <v>5.8530788152177937E-4</v>
+        <v>5.8530788152172386E-4</v>
       </c>
       <c r="K11" s="86">
         <f t="shared" si="2"/>
-        <v>3.4258531617151332E-7</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+        <v>3.4258531617144831E-7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A12" s="84">
         <f>'Pràctica A'!E126</f>
         <v>0.53505538888888882</v>
@@ -21147,18 +21147,18 @@
       </c>
       <c r="F12" s="35">
         <f t="shared" si="0"/>
-        <v>0.30496993009569001</v>
+        <v>0.30496993009569007</v>
       </c>
       <c r="J12" s="86">
         <f t="shared" si="1"/>
-        <v>8.4806990430996709E-4</v>
+        <v>8.4806990430991158E-4</v>
       </c>
       <c r="K12" s="86">
         <f t="shared" si="2"/>
-        <v>7.1922256259631673E-7</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+        <v>7.1922256259622261E-7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A13" s="84">
         <f>'Pràctica A'!E127</f>
         <v>0.535015388888889</v>
@@ -21176,18 +21176,18 @@
       </c>
       <c r="F13" s="35">
         <f t="shared" si="0"/>
-        <v>0.30456400878169759</v>
+        <v>0.30456400878169765</v>
       </c>
       <c r="J13" s="86">
         <f t="shared" si="1"/>
-        <v>5.6299121830238885E-4</v>
+        <v>5.6299121830233334E-4</v>
       </c>
       <c r="K13" s="86">
         <f t="shared" si="2"/>
-        <v>3.1695911188560805E-7</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+        <v>3.1695911188554558E-7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A14" s="84">
         <f>'Pràctica A'!E128</f>
         <v>0.52666461111111118</v>
@@ -21205,18 +21205,18 @@
       </c>
       <c r="F14" s="35">
         <f t="shared" si="0"/>
-        <v>0.30212279136726888</v>
+        <v>0.30212279136726894</v>
       </c>
       <c r="J14" s="86">
         <f t="shared" si="1"/>
-        <v>2.3320863273113002E-4</v>
+        <v>2.3320863273107451E-4</v>
       </c>
       <c r="K14" s="86">
         <f t="shared" si="2"/>
-        <v>5.4386266380323087E-8</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+        <v>5.4386266380297193E-8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A15" s="84">
         <f>'Pràctica A'!E129</f>
         <v>0.50680344444444447</v>
@@ -21234,18 +21234,18 @@
       </c>
       <c r="F15" s="35">
         <f t="shared" si="0"/>
-        <v>0.29558648814795901</v>
+        <v>0.29558648814795907</v>
       </c>
       <c r="J15" s="86">
         <f t="shared" si="1"/>
-        <v>-2.1648814795899307E-4</v>
+        <v>-2.1648814795904858E-4</v>
       </c>
       <c r="K15" s="86">
         <f t="shared" si="2"/>
-        <v>4.6867118206714874E-8</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+        <v>4.6867118206738908E-8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A16" s="84">
         <f>'Pràctica A'!E130</f>
         <v>0.47530083333333328</v>
@@ -21263,18 +21263,18 @@
       </c>
       <c r="F16" s="35">
         <f t="shared" si="0"/>
-        <v>0.28366528932379464</v>
+        <v>0.2836652893237947</v>
       </c>
       <c r="J16" s="86">
         <f t="shared" si="1"/>
-        <v>-6.7289323794628153E-5</v>
+        <v>-6.7289323794683664E-5</v>
       </c>
       <c r="K16" s="86">
         <f t="shared" si="2"/>
-        <v>4.5278530967383106E-9</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+        <v>4.5278530967457809E-9</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A17" s="84">
         <f>'Pràctica A'!E131</f>
         <v>0.4366733888888889</v>
@@ -21292,18 +21292,18 @@
       </c>
       <c r="F17" s="35">
         <f t="shared" si="0"/>
-        <v>0.26621367765269421</v>
+        <v>0.26621367765269427</v>
       </c>
       <c r="J17" s="86">
         <f t="shared" si="1"/>
-        <v>4.0322347305776773E-5</v>
+        <v>4.0322347305721262E-5</v>
       </c>
       <c r="K17" s="86">
         <f t="shared" si="2"/>
-        <v>1.6258916922476833E-9</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
+        <v>1.6258916922432066E-9</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A18" s="84">
         <f>'Pràctica A'!E132</f>
         <v>0.3961257777777778</v>
@@ -21321,18 +21321,18 @@
       </c>
       <c r="F18" s="35">
         <f t="shared" si="0"/>
-        <v>0.24522637501843633</v>
+        <v>0.24522637501843636</v>
       </c>
       <c r="J18" s="86">
         <f t="shared" si="1"/>
-        <v>9.862498156365529E-5</v>
+        <v>9.8624981563627534E-5</v>
       </c>
       <c r="K18" s="86">
         <f t="shared" si="2"/>
-        <v>9.7268869884313452E-9</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>9.7268869884258709E-9</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D19" s="35">
         <f>'Pràctica A'!J67</f>
         <v>0.22297400000000001</v>
@@ -21342,41 +21342,41 @@
       </c>
       <c r="F19" s="35">
         <f t="shared" si="0"/>
-        <v>0.22307622735932153</v>
+        <v>0.22307622735932156</v>
       </c>
       <c r="J19" s="86">
         <f t="shared" si="1"/>
-        <v>-1.0222735932152727E-4</v>
+        <v>-1.0222735932155502E-4</v>
       </c>
       <c r="K19" s="86">
         <f t="shared" si="2"/>
-        <v>1.0450432993852648E-8</v>
+        <v>1.0450432993858323E-8</v>
       </c>
       <c r="N19" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
       <c r="N20" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.2">
       <c r="N21" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.2">
       <c r="D23" s="6" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.2">
       <c r="G25" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.2">
       <c r="D26" s="85" t="s">
         <v>99</v>
       </c>
@@ -21408,7 +21408,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.2">
       <c r="D27" s="35">
         <f>'Pràctica A'!I53</f>
         <v>0.297182</v>
@@ -21443,7 +21443,7 @@
       </c>
       <c r="N27" s="74"/>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.2">
       <c r="D28" s="35">
         <f>'Pràctica A'!I54</f>
         <v>0.326104</v>
@@ -21464,7 +21464,7 @@
         <v>1.0434684265941686E-5</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.2">
       <c r="D29" s="35">
         <f>'Pràctica A'!I55</f>
         <v>0.35388999999999998</v>
@@ -21473,7 +21473,7 @@
         <v>540</v>
       </c>
       <c r="F29" s="35">
-        <f t="shared" ref="F29:F41" si="5">A6*$G$27 + B6*$H$27 +$I$27</f>
+        <f>A6*$G$27 + B6*$H$27 +$I$27</f>
         <v>0.35524151936846143</v>
       </c>
       <c r="J29" s="86">
@@ -21485,7 +21485,7 @@
         <v>1.82660460332644E-6</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.2">
       <c r="D30" s="35">
         <f>'Pràctica A'!I56</f>
         <v>0.37645499999999998</v>
@@ -21494,7 +21494,7 @@
         <v>535</v>
       </c>
       <c r="F30" s="35">
-        <f t="shared" si="5"/>
+        <f>A7*$G$27 + B7*$H$27 +$I$27</f>
         <v>0.37813465991220852</v>
       </c>
       <c r="J30" s="86">
@@ -21506,7 +21506,7 @@
         <v>2.82125742068037E-6</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.2">
       <c r="D31" s="35">
         <f>'Pràctica A'!I57</f>
         <v>0.39011699999999999</v>
@@ -21515,7 +21515,7 @@
         <v>530</v>
       </c>
       <c r="F31" s="35">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="F29:F41" si="5">A8*$G$27 + B8*$H$27 +$I$27</f>
         <v>0.39146544547198636</v>
       </c>
       <c r="J31" s="86">
@@ -21527,7 +21527,7 @@
         <v>1.818305190920545E-6</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.2">
       <c r="D32" s="35">
         <f>'Pràctica A'!I58</f>
         <v>0.39472099999999999</v>
@@ -21536,7 +21536,7 @@
         <v>525</v>
       </c>
       <c r="F32" s="35">
-        <f t="shared" si="5"/>
+        <f>A9*$G$27 + B9*$H$27 +$I$27</f>
         <v>0.39524318931534475</v>
       </c>
       <c r="J32" s="86">
@@ -21548,7 +21548,7 @@
         <v>2.7268168106022562E-7</v>
       </c>
     </row>
-    <row r="33" spans="4:14" x14ac:dyDescent="0.3">
+    <row r="33" spans="4:14" x14ac:dyDescent="0.2">
       <c r="D33" s="35">
         <f>'Pràctica A'!I59</f>
         <v>0.39447599999999999</v>
@@ -21557,7 +21557,7 @@
         <v>520</v>
       </c>
       <c r="F33" s="35">
-        <f t="shared" si="5"/>
+        <f>A10*$G$27 + B10*$H$27 +$I$27</f>
         <v>0.39377993336186712</v>
       </c>
       <c r="J33" s="86">
@@ -21569,7 +21569,7 @@
         <v>4.8450876472160283E-7</v>
       </c>
     </row>
-    <row r="34" spans="4:14" x14ac:dyDescent="0.3">
+    <row r="34" spans="4:14" x14ac:dyDescent="0.2">
       <c r="D34" s="35">
         <f>'Pràctica A'!I60</f>
         <v>0.39258900000000002</v>
@@ -21578,7 +21578,7 @@
         <v>515</v>
       </c>
       <c r="F34" s="35">
-        <f t="shared" si="5"/>
+        <f>A11*$G$27 + B11*$H$27 +$I$27</f>
         <v>0.39162345906878571</v>
       </c>
       <c r="J34" s="86">
@@ -21590,7 +21590,7 @@
         <v>9.3226928985020629E-7</v>
       </c>
     </row>
-    <row r="35" spans="4:14" x14ac:dyDescent="0.3">
+    <row r="35" spans="4:14" x14ac:dyDescent="0.2">
       <c r="D35" s="35">
         <f>'Pràctica A'!I61</f>
         <v>0.38922899999999999</v>
@@ -21599,7 +21599,7 @@
         <v>510</v>
       </c>
       <c r="F35" s="35">
-        <f t="shared" si="5"/>
+        <f>A12*$G$27 + B12*$H$27 +$I$27</f>
         <v>0.3883271673371036</v>
       </c>
       <c r="J35" s="86">
@@ -21611,7 +21611,7 @@
         <v>8.1330215186680416E-7</v>
       </c>
     </row>
-    <row r="36" spans="4:14" x14ac:dyDescent="0.3">
+    <row r="36" spans="4:14" x14ac:dyDescent="0.2">
       <c r="D36" s="35">
         <f>'Pràctica A'!I62</f>
         <v>0.38248500000000002</v>
@@ -21620,7 +21620,7 @@
         <v>505</v>
       </c>
       <c r="F36" s="35">
-        <f t="shared" si="5"/>
+        <f>A13*$G$27 + B13*$H$27 +$I$27</f>
         <v>0.38200488609006344</v>
       </c>
       <c r="J36" s="86">
@@ -21632,7 +21632,7 @@
         <v>2.3050936651458543E-7</v>
       </c>
     </row>
-    <row r="37" spans="4:14" x14ac:dyDescent="0.3">
+    <row r="37" spans="4:14" x14ac:dyDescent="0.2">
       <c r="D37" s="35">
         <f>'Pràctica A'!I63</f>
         <v>0.370971</v>
@@ -21641,7 +21641,7 @@
         <v>500</v>
       </c>
       <c r="F37" s="35">
-        <f t="shared" si="5"/>
+        <f>A14*$G$27 + B14*$H$27 +$I$27</f>
         <v>0.37085157274443048</v>
       </c>
       <c r="J37" s="86">
@@ -21653,7 +21653,7 @@
         <v>1.4262869372866318E-8</v>
       </c>
     </row>
-    <row r="38" spans="4:14" x14ac:dyDescent="0.3">
+    <row r="38" spans="4:14" x14ac:dyDescent="0.2">
       <c r="D38" s="35">
         <f>'Pràctica A'!I64</f>
         <v>0.35401199999999999</v>
@@ -21674,7 +21674,7 @@
         <v>6.6927356578563071E-8</v>
       </c>
     </row>
-    <row r="39" spans="4:14" x14ac:dyDescent="0.3">
+    <row r="39" spans="4:14" x14ac:dyDescent="0.2">
       <c r="D39" s="35">
         <f>'Pràctica A'!I65</f>
         <v>0.330733</v>
@@ -21683,7 +21683,7 @@
         <v>490</v>
       </c>
       <c r="F39" s="35">
-        <f t="shared" si="5"/>
+        <f>A16*$G$27 + B16*$H$27 +$I$27</f>
         <v>0.33042332697460081</v>
       </c>
       <c r="J39" s="86">
@@ -21695,7 +21695,7 @@
         <v>9.5897382659889274E-8</v>
       </c>
     </row>
-    <row r="40" spans="4:14" x14ac:dyDescent="0.3">
+    <row r="40" spans="4:14" x14ac:dyDescent="0.2">
       <c r="D40" s="35">
         <f>'Pràctica A'!I66</f>
         <v>0.30288399999999999</v>
@@ -21704,7 +21704,7 @@
         <v>485</v>
       </c>
       <c r="F40" s="35">
-        <f t="shared" si="5"/>
+        <f>A17*$G$27 + B17*$H$27 +$I$27</f>
         <v>0.30288675161909179</v>
       </c>
       <c r="J40" s="86">
@@ -21716,7 +21716,7 @@
         <v>7.5714076263631163E-12</v>
       </c>
     </row>
-    <row r="41" spans="4:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="4:14" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D41" s="35">
         <f>'Pràctica A'!I67</f>
         <v>0.27276800000000001</v>
@@ -21725,7 +21725,7 @@
         <v>480</v>
       </c>
       <c r="F41" s="35">
-        <f t="shared" si="5"/>
+        <f>A18*$G$27 + B18*$H$27 +$I$27</f>
         <v>0.27367030490010241</v>
       </c>
       <c r="J41" s="86">
@@ -21740,22 +21740,22 @@
         <v>168</v>
       </c>
     </row>
-    <row r="42" spans="4:14" x14ac:dyDescent="0.3">
+    <row r="42" spans="4:14" x14ac:dyDescent="0.2">
       <c r="N42" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="46" spans="4:14" x14ac:dyDescent="0.3">
+    <row r="46" spans="4:14" x14ac:dyDescent="0.2">
       <c r="D46" s="6" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="48" spans="4:14" x14ac:dyDescent="0.3">
+    <row r="48" spans="4:14" x14ac:dyDescent="0.2">
       <c r="G48" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="49" spans="4:14" x14ac:dyDescent="0.3">
+    <row r="49" spans="4:14" x14ac:dyDescent="0.2">
       <c r="D49" s="85" t="s">
         <v>99</v>
       </c>
@@ -21787,7 +21787,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="50" spans="4:14" x14ac:dyDescent="0.3">
+    <row r="50" spans="4:14" x14ac:dyDescent="0.2">
       <c r="D50" s="78">
         <f>'Pràctica A'!H53</f>
         <v>0.22475500000000001</v>
@@ -21816,12 +21816,12 @@
         <f>J50^2</f>
         <v>7.5788950307693888E-7</v>
       </c>
-      <c r="L50">
+      <c r="L50" s="86">
         <f>SUM(K50:K64)</f>
         <v>3.2745938802101474E-6</v>
       </c>
     </row>
-    <row r="51" spans="4:14" x14ac:dyDescent="0.3">
+    <row r="51" spans="4:14" x14ac:dyDescent="0.2">
       <c r="D51" s="78">
         <f>'Pràctica A'!H54</f>
         <v>0.242007</v>
@@ -21842,7 +21842,7 @@
         <v>1.6135805596460055E-6</v>
       </c>
     </row>
-    <row r="52" spans="4:14" x14ac:dyDescent="0.3">
+    <row r="52" spans="4:14" x14ac:dyDescent="0.2">
       <c r="D52" s="78">
         <f>'Pràctica A'!H55</f>
         <v>0.257577</v>
@@ -21863,7 +21863,7 @@
         <v>3.3142394113152043E-7</v>
       </c>
     </row>
-    <row r="53" spans="4:14" x14ac:dyDescent="0.3">
+    <row r="53" spans="4:14" x14ac:dyDescent="0.2">
       <c r="D53" s="78">
         <f>'Pràctica A'!H56</f>
         <v>0.27008300000000002</v>
@@ -21884,7 +21884,7 @@
         <v>1.4185577736340409E-7</v>
       </c>
     </row>
-    <row r="54" spans="4:14" x14ac:dyDescent="0.3">
+    <row r="54" spans="4:14" x14ac:dyDescent="0.2">
       <c r="D54" s="78">
         <f>'Pràctica A'!H57</f>
         <v>0.27764899999999998</v>
@@ -21905,7 +21905,7 @@
         <v>3.6409305304718177E-8</v>
       </c>
     </row>
-    <row r="55" spans="4:14" x14ac:dyDescent="0.3">
+    <row r="55" spans="4:14" x14ac:dyDescent="0.2">
       <c r="D55" s="78">
         <f>'Pràctica A'!H58</f>
         <v>0.28016999999999997</v>
@@ -21926,7 +21926,7 @@
         <v>1.8218592554444347E-9</v>
       </c>
     </row>
-    <row r="56" spans="4:14" x14ac:dyDescent="0.3">
+    <row r="56" spans="4:14" x14ac:dyDescent="0.2">
       <c r="D56" s="78">
         <f>'Pràctica A'!H59</f>
         <v>0.27915899999999999</v>
@@ -21947,7 +21947,7 @@
         <v>1.5809138145031322E-7</v>
       </c>
     </row>
-    <row r="57" spans="4:14" x14ac:dyDescent="0.3">
+    <row r="57" spans="4:14" x14ac:dyDescent="0.2">
       <c r="D57" s="78">
         <f>'Pràctica A'!H60</f>
         <v>0.27611999999999998</v>
@@ -21968,7 +21968,7 @@
         <v>1.0119934692416721E-7</v>
       </c>
     </row>
-    <row r="58" spans="4:14" x14ac:dyDescent="0.3">
+    <row r="58" spans="4:14" x14ac:dyDescent="0.2">
       <c r="D58" s="78">
         <f>'Pràctica A'!H61</f>
         <v>0.271117</v>
@@ -21989,7 +21989,7 @@
         <v>4.9143335076515798E-8</v>
       </c>
     </row>
-    <row r="59" spans="4:14" x14ac:dyDescent="0.3">
+    <row r="59" spans="4:14" x14ac:dyDescent="0.2">
       <c r="D59" s="78">
         <f>'Pràctica A'!H62</f>
         <v>0.26358399999999998</v>
@@ -22010,7 +22010,7 @@
         <v>3.8949743959035961E-10</v>
       </c>
     </row>
-    <row r="60" spans="4:14" x14ac:dyDescent="0.3">
+    <row r="60" spans="4:14" x14ac:dyDescent="0.2">
       <c r="D60" s="78">
         <f>'Pràctica A'!H63</f>
         <v>0.25330399999999997</v>
@@ -22031,7 +22031,7 @@
         <v>1.3533473995029948E-8</v>
       </c>
     </row>
-    <row r="61" spans="4:14" x14ac:dyDescent="0.3">
+    <row r="61" spans="4:14" x14ac:dyDescent="0.2">
       <c r="D61" s="78">
         <f>'Pràctica A'!H64</f>
         <v>0.240283</v>
@@ -22052,7 +22052,7 @@
         <v>1.282127636715972E-9</v>
       </c>
     </row>
-    <row r="62" spans="4:14" x14ac:dyDescent="0.3">
+    <row r="62" spans="4:14" x14ac:dyDescent="0.2">
       <c r="D62" s="78">
         <f>'Pràctica A'!H65</f>
         <v>0.22359499999999999</v>
@@ -22073,7 +22073,7 @@
         <v>2.5886802433251941E-8</v>
       </c>
     </row>
-    <row r="63" spans="4:14" x14ac:dyDescent="0.3">
+    <row r="63" spans="4:14" x14ac:dyDescent="0.2">
       <c r="D63" s="78">
         <f>'Pràctica A'!H66</f>
         <v>0.20483599999999999</v>
@@ -22094,7 +22094,7 @@
         <v>3.4047492987281788E-9</v>
       </c>
     </row>
-    <row r="64" spans="4:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="4:14" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D64" s="78">
         <f>'Pràctica A'!H67</f>
         <v>0.18429799999999999</v>
@@ -22118,7 +22118,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="65" spans="14:14" x14ac:dyDescent="0.3">
+    <row r="65" spans="14:14" x14ac:dyDescent="0.2">
       <c r="N65" t="s">
         <v>169</v>
       </c>
@@ -22132,21 +22132,21 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB4820DD-6969-4040-93C5-649CCF9DF955}">
   <dimension ref="A2:V54"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="22.5546875" customWidth="1"/>
-    <col min="2" max="2" width="18.77734375" customWidth="1"/>
-    <col min="3" max="4" width="15.44140625" customWidth="1"/>
+    <col min="1" max="1" width="22.5" customWidth="1"/>
+    <col min="2" max="2" width="18.83203125" customWidth="1"/>
+    <col min="3" max="4" width="15.5" customWidth="1"/>
     <col min="5" max="5" width="18.33203125" customWidth="1"/>
-    <col min="8" max="8" width="21.21875" customWidth="1"/>
+    <col min="8" max="8" width="21.1640625" customWidth="1"/>
     <col min="9" max="9" width="18.6640625" customWidth="1"/>
-    <col min="10" max="10" width="18.109375" customWidth="1"/>
+    <col min="10" max="10" width="18.1640625" customWidth="1"/>
     <col min="12" max="12" width="18" customWidth="1"/>
     <col min="13" max="13" width="17.6640625" customWidth="1"/>
-    <col min="18" max="18" width="19.109375" customWidth="1"/>
+    <col min="18" max="18" width="19.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A2" cm="1">
         <f t="array" ref="A2:J18">'Pràctica A'!A51:J67</f>
         <v>0</v>
@@ -22213,7 +22213,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A3" s="93" t="str">
         <v>Longitud d'ona (nm)</v>
       </c>
@@ -22278,7 +22278,7 @@
         <v>std</v>
       </c>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A4" s="94">
         <v>550</v>
       </c>
@@ -22343,7 +22343,7 @@
         <v>1.1478669154776378E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="64">
         <v>545</v>
       </c>
@@ -22408,7 +22408,7 @@
         <v>5.3504413109783271E-4</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A6" s="64">
         <v>540</v>
       </c>
@@ -22473,7 +22473,7 @@
         <v>2.1089869632607266E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A7" s="64">
         <v>535</v>
       </c>
@@ -22538,7 +22538,7 @@
         <v>2.600429501561732E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A8" s="64">
         <v>530</v>
       </c>
@@ -22603,7 +22603,7 @@
         <v>3.0020418681074995E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A9" s="64">
         <v>525</v>
       </c>
@@ -22668,7 +22668,7 @@
         <v>3.3155009942077547E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A10" s="64">
         <v>520</v>
       </c>
@@ -22733,7 +22733,7 @@
         <v>3.6569031566011198E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A11" s="64">
         <v>515</v>
       </c>
@@ -22798,7 +22798,7 @@
         <v>4.066007964822501E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A12" s="64">
         <v>510</v>
       </c>
@@ -22863,7 +22863,7 @@
         <v>4.5208037785925879E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A13" s="64">
         <v>505</v>
       </c>
@@ -22928,7 +22928,7 @@
         <v>4.9589177671346511E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A14" s="64">
         <v>500</v>
       </c>
@@ -22993,7 +22993,7 @@
         <v>5.3455500719012713E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A15" s="64">
         <v>495</v>
       </c>
@@ -23058,7 +23058,7 @@
         <v>5.5824204298785991E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A16" s="64">
         <v>490</v>
       </c>
@@ -23123,7 +23123,7 @@
         <v>5.6940385290963132E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A17" s="64">
         <v>485</v>
       </c>
@@ -23188,7 +23188,7 @@
         <v>5.7905543123725867E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:22" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A18" s="65">
         <v>480</v>
       </c>
@@ -23253,23 +23253,23 @@
         <v>5.8951433006174468E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:22" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:22" ht="17" x14ac:dyDescent="0.2">
       <c r="A20" s="85" t="s">
         <v>117</v>
       </c>
       <c r="B20" s="103" t="s">
         <v>127</v>
       </c>
-      <c r="C20" s="133" t="s">
+      <c r="C20" s="134" t="s">
         <v>123</v>
       </c>
-      <c r="D20" s="133"/>
-      <c r="F20" s="133" t="s">
+      <c r="D20" s="134"/>
+      <c r="F20" s="134" t="s">
         <v>131</v>
       </c>
-      <c r="G20" s="133"/>
-    </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="G20" s="134"/>
+    </row>
+    <row r="21" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A21" s="48">
         <v>550</v>
       </c>
@@ -23331,16 +23331,16 @@
         <v>0.3961257777777778</v>
       </c>
     </row>
-    <row r="22" spans="1:22" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:22" ht="17" x14ac:dyDescent="0.2">
       <c r="A22" s="26">
         <v>545</v>
       </c>
       <c r="C22" s="99">
-        <f t="shared" ref="C22:C35" si="0">U5</f>
+        <f>U5</f>
         <v>0.39884833333333336</v>
       </c>
       <c r="D22" s="100">
-        <f t="shared" ref="D22:D35" si="1">P5</f>
+        <f t="shared" ref="D22:D35" si="0">P5</f>
         <v>0.39739661111111108</v>
       </c>
       <c r="E22" s="101" t="s">
@@ -23392,39 +23392,39 @@
         <v>0.25695174999999998</v>
       </c>
     </row>
-    <row r="23" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A23" s="26">
         <v>540</v>
       </c>
       <c r="C23" s="99">
+        <f t="shared" ref="C22:C35" si="1">U6</f>
+        <v>0.45877661111111112</v>
+      </c>
+      <c r="D23" s="100">
         <f t="shared" si="0"/>
-        <v>0.45877661111111112</v>
-      </c>
-      <c r="D23" s="100">
-        <f t="shared" si="1"/>
         <v>0.40979361111111112</v>
       </c>
       <c r="F23" s="107"/>
       <c r="G23" s="107"/>
     </row>
-    <row r="24" spans="1:22" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:22" ht="17" x14ac:dyDescent="0.2">
       <c r="A24" s="26">
         <v>535</v>
       </c>
       <c r="C24" s="99">
+        <f t="shared" si="1"/>
+        <v>0.50119555555555551</v>
+      </c>
+      <c r="D24" s="100">
         <f t="shared" si="0"/>
-        <v>0.50119555555555551</v>
-      </c>
-      <c r="D24" s="100">
-        <f t="shared" si="1"/>
         <v>0.41851666666666665</v>
       </c>
-      <c r="F24" s="133" t="s">
+      <c r="F24" s="134" t="s">
         <v>134</v>
       </c>
-      <c r="G24" s="133"/>
-    </row>
-    <row r="25" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="G24" s="134"/>
+    </row>
+    <row r="25" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A25" s="26">
         <v>530</v>
       </c>
@@ -23432,11 +23432,11 @@
         <v>124</v>
       </c>
       <c r="C25" s="99">
+        <f t="shared" si="1"/>
+        <v>0.52526161111111103</v>
+      </c>
+      <c r="D25" s="100">
         <f t="shared" si="0"/>
-        <v>0.52526161111111103</v>
-      </c>
-      <c r="D25" s="100">
-        <f t="shared" si="1"/>
         <v>0.4244694444444444</v>
       </c>
       <c r="E25" s="101"/>
@@ -23448,16 +23448,16 @@
         <v>2.7480455242698456</v>
       </c>
     </row>
-    <row r="26" spans="1:22" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:22" ht="17" x14ac:dyDescent="0.2">
       <c r="A26" s="26">
         <v>525</v>
       </c>
       <c r="C26" s="99">
+        <f t="shared" si="1"/>
+        <v>0.53149944444444441</v>
+      </c>
+      <c r="D26" s="100">
         <f t="shared" si="0"/>
-        <v>0.53149944444444441</v>
-      </c>
-      <c r="D26" s="100">
-        <f t="shared" si="1"/>
         <v>0.42695733333333336</v>
       </c>
       <c r="E26" s="101" t="s">
@@ -23470,48 +23470,48 @@
         <v>2.1624051604461116</v>
       </c>
     </row>
-    <row r="27" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A27" s="26">
         <v>520</v>
       </c>
       <c r="C27" s="99">
+        <f t="shared" si="1"/>
+        <v>0.53050805555555547</v>
+      </c>
+      <c r="D27" s="100">
         <f t="shared" si="0"/>
-        <v>0.53050805555555547</v>
-      </c>
-      <c r="D27" s="100">
-        <f t="shared" si="1"/>
         <v>0.42403333333333332</v>
       </c>
       <c r="F27" s="107"/>
       <c r="G27" s="107"/>
     </row>
-    <row r="28" spans="1:22" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:22" ht="17" x14ac:dyDescent="0.2">
       <c r="A28" s="26">
         <v>515</v>
       </c>
       <c r="C28" s="99">
+        <f t="shared" si="1"/>
+        <v>0.53185700000000002</v>
+      </c>
+      <c r="D28" s="100">
         <f t="shared" si="0"/>
-        <v>0.53185700000000002</v>
-      </c>
-      <c r="D28" s="100">
-        <f t="shared" si="1"/>
         <v>0.41585772222222223</v>
       </c>
-      <c r="F28" s="133" t="s">
+      <c r="F28" s="134" t="s">
         <v>135</v>
       </c>
-      <c r="G28" s="133"/>
-    </row>
-    <row r="29" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="G28" s="134"/>
+    </row>
+    <row r="29" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A29" s="26">
         <v>510</v>
       </c>
       <c r="C29" s="99">
+        <f t="shared" si="1"/>
+        <v>0.53505538888888882</v>
+      </c>
+      <c r="D29" s="100">
         <f t="shared" si="0"/>
-        <v>0.53505538888888882</v>
-      </c>
-      <c r="D29" s="100">
-        <f t="shared" si="1"/>
         <v>0.40179716666666665</v>
       </c>
       <c r="E29" s="101"/>
@@ -23523,16 +23523,16 @@
         <v>-20.98197685873151</v>
       </c>
     </row>
-    <row r="30" spans="1:22" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:22" ht="17" x14ac:dyDescent="0.2">
       <c r="A30" s="26">
         <v>505</v>
       </c>
       <c r="C30" s="99">
+        <f t="shared" si="1"/>
+        <v>0.535015388888889</v>
+      </c>
+      <c r="D30" s="100">
         <f t="shared" si="0"/>
-        <v>0.535015388888889</v>
-      </c>
-      <c r="D30" s="100">
-        <f t="shared" si="1"/>
         <v>0.38332472222222219</v>
       </c>
       <c r="E30" s="101" t="s">
@@ -23545,48 +23545,48 @@
         <v>27.126936556546582</v>
       </c>
     </row>
-    <row r="31" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A31" s="26">
         <v>500</v>
       </c>
       <c r="C31" s="99">
+        <f t="shared" si="1"/>
+        <v>0.52666461111111118</v>
+      </c>
+      <c r="D31" s="100">
         <f t="shared" si="0"/>
-        <v>0.52666461111111118</v>
-      </c>
-      <c r="D31" s="100">
-        <f t="shared" si="1"/>
         <v>0.36212994444444441</v>
       </c>
       <c r="F31" s="107"/>
       <c r="G31" s="107"/>
     </row>
-    <row r="32" spans="1:22" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:22" ht="17" x14ac:dyDescent="0.2">
       <c r="A32" s="26">
         <v>495</v>
       </c>
       <c r="C32" s="99">
+        <f t="shared" si="1"/>
+        <v>0.50680344444444447</v>
+      </c>
+      <c r="D32" s="100">
         <f t="shared" si="0"/>
-        <v>0.50680344444444447</v>
-      </c>
-      <c r="D32" s="100">
-        <f t="shared" si="1"/>
         <v>0.33935088888888892</v>
       </c>
-      <c r="F32" s="133" t="s">
+      <c r="F32" s="134" t="s">
         <v>138</v>
       </c>
-      <c r="G32" s="133"/>
-    </row>
-    <row r="33" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="G32" s="134"/>
+    </row>
+    <row r="33" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A33" s="26">
         <v>490</v>
       </c>
       <c r="C33" s="99">
+        <f t="shared" si="1"/>
+        <v>0.47530083333333328</v>
+      </c>
+      <c r="D33" s="100">
         <f t="shared" si="0"/>
-        <v>0.47530083333333328</v>
-      </c>
-      <c r="D33" s="100">
-        <f t="shared" si="1"/>
         <v>0.31432761111111113</v>
       </c>
       <c r="E33" s="101"/>
@@ -23637,16 +23637,16 @@
         <v>1.1488688058689114</v>
       </c>
     </row>
-    <row r="34" spans="1:20" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:20" ht="17" x14ac:dyDescent="0.2">
       <c r="A34" s="26">
         <v>485</v>
       </c>
       <c r="C34" s="99">
+        <f t="shared" si="1"/>
+        <v>0.4366733888888889</v>
+      </c>
+      <c r="D34" s="100">
         <f t="shared" si="0"/>
-        <v>0.4366733888888889</v>
-      </c>
-      <c r="D34" s="100">
-        <f t="shared" si="1"/>
         <v>0.28678011111111107</v>
       </c>
       <c r="E34" s="101" t="s">
@@ -23698,54 +23698,54 @@
         <v>-1.3411880821367372</v>
       </c>
     </row>
-    <row r="35" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:20" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A35" s="27">
         <v>480</v>
       </c>
       <c r="C35" s="99">
+        <f t="shared" si="1"/>
+        <v>0.3961257777777778</v>
+      </c>
+      <c r="D35" s="100">
         <f t="shared" si="0"/>
-        <v>0.3961257777777778</v>
-      </c>
-      <c r="D35" s="100">
-        <f t="shared" si="1"/>
         <v>0.25695174999999998</v>
       </c>
       <c r="F35" s="107"/>
       <c r="G35" s="107"/>
     </row>
-    <row r="37" spans="1:20" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C37" s="134" t="s">
+    <row r="37" spans="1:20" ht="22.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C37" s="135" t="s">
         <v>114</v>
       </c>
-      <c r="D37" s="135"/>
-      <c r="E37" s="135"/>
-      <c r="F37" s="135"/>
-      <c r="G37" s="135"/>
-      <c r="H37" s="135"/>
-      <c r="I37" s="135"/>
-      <c r="J37" s="135"/>
-      <c r="K37" s="135"/>
-      <c r="L37" s="135"/>
-      <c r="M37" s="135"/>
-    </row>
-    <row r="38" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="C38" s="134" t="s">
+      <c r="D37" s="133"/>
+      <c r="E37" s="133"/>
+      <c r="F37" s="133"/>
+      <c r="G37" s="133"/>
+      <c r="H37" s="133"/>
+      <c r="I37" s="133"/>
+      <c r="J37" s="133"/>
+      <c r="K37" s="133"/>
+      <c r="L37" s="133"/>
+      <c r="M37" s="133"/>
+    </row>
+    <row r="38" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="C38" s="135" t="s">
         <v>76</v>
       </c>
-      <c r="D38" s="135"/>
-      <c r="E38" s="135"/>
-      <c r="G38" s="135" t="s">
+      <c r="D38" s="133"/>
+      <c r="E38" s="133"/>
+      <c r="G38" s="133" t="s">
         <v>77</v>
       </c>
-      <c r="H38" s="135"/>
-      <c r="I38" s="135"/>
-      <c r="K38" s="135" t="s">
+      <c r="H38" s="133"/>
+      <c r="I38" s="133"/>
+      <c r="K38" s="133" t="s">
         <v>91</v>
       </c>
-      <c r="L38" s="135"/>
-      <c r="M38" s="135"/>
-    </row>
-    <row r="39" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="L38" s="133"/>
+      <c r="M38" s="133"/>
+    </row>
+    <row r="39" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A39" s="74" t="s">
         <v>140</v>
       </c>
@@ -23768,7 +23768,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="40" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C40" s="109">
         <f>'Pràctica A'!H53</f>
         <v>0.22475500000000001</v>
@@ -23794,7 +23794,7 @@
         <v>0.46445305485432048</v>
       </c>
     </row>
-    <row r="41" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C41" s="109">
         <f>'Pràctica A'!H54</f>
         <v>0.242007</v>
@@ -23826,7 +23826,7 @@
         <v>0.14175237609521807</v>
       </c>
     </row>
-    <row r="42" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C42" s="109">
         <f>'Pràctica A'!H55</f>
         <v>0.257577</v>
@@ -23840,7 +23840,7 @@
         <v>0.27023000000000003</v>
       </c>
     </row>
-    <row r="43" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C43" s="109">
         <f>'Pràctica A'!H56</f>
         <v>0.27008300000000002</v>
@@ -23854,7 +23854,7 @@
         <v>0.29030800000000001</v>
       </c>
     </row>
-    <row r="44" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C44" s="109">
         <f>'Pràctica A'!H57</f>
         <v>0.27764899999999998</v>
@@ -23868,7 +23868,7 @@
         <v>0.30221599999999998</v>
       </c>
     </row>
-    <row r="45" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C45" s="109">
         <f>'Pràctica A'!H58</f>
         <v>0.28016999999999997</v>
@@ -23882,7 +23882,7 @@
         <v>0.30606499999999998</v>
       </c>
     </row>
-    <row r="46" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C46" s="109">
         <f>'Pràctica A'!H59</f>
         <v>0.27915899999999999</v>
@@ -23896,7 +23896,7 @@
         <v>0.30602099999999999</v>
       </c>
     </row>
-    <row r="47" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C47" s="99">
         <f>'Pràctica A'!H60</f>
         <v>0.27611999999999998</v>
@@ -23913,7 +23913,7 @@
       </c>
       <c r="L47" s="107"/>
     </row>
-    <row r="48" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C48" s="99">
         <f>'Pràctica A'!H61</f>
         <v>0.271117</v>
@@ -23930,7 +23930,7 @@
       </c>
       <c r="L48" s="107"/>
     </row>
-    <row r="49" spans="3:12" x14ac:dyDescent="0.3">
+    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C49" s="99">
         <f>'Pràctica A'!H62</f>
         <v>0.26358399999999998</v>
@@ -23947,7 +23947,7 @@
       </c>
       <c r="L49" s="107"/>
     </row>
-    <row r="50" spans="3:12" x14ac:dyDescent="0.3">
+    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C50" s="99">
         <f>'Pràctica A'!H63</f>
         <v>0.25330399999999997</v>
@@ -23964,7 +23964,7 @@
       </c>
       <c r="L50" s="108"/>
     </row>
-    <row r="51" spans="3:12" x14ac:dyDescent="0.3">
+    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C51" s="99">
         <f>'Pràctica A'!H64</f>
         <v>0.240283</v>
@@ -23981,7 +23981,7 @@
       </c>
       <c r="L51" s="108"/>
     </row>
-    <row r="52" spans="3:12" x14ac:dyDescent="0.3">
+    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C52" s="99">
         <f>'Pràctica A'!H65</f>
         <v>0.22359499999999999</v>
@@ -23998,7 +23998,7 @@
       </c>
       <c r="L52" s="108"/>
     </row>
-    <row r="53" spans="3:12" x14ac:dyDescent="0.3">
+    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C53" s="99">
         <f>'Pràctica A'!H66</f>
         <v>0.20483599999999999</v>
@@ -24015,7 +24015,7 @@
       </c>
       <c r="L53" s="108"/>
     </row>
-    <row r="54" spans="3:12" x14ac:dyDescent="0.3">
+    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C54" s="99">
         <f>'Pràctica A'!H67</f>
         <v>0.18429799999999999</v>
@@ -24051,7 +24051,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF805755-B3F4-A041-8801-ACD56112111B}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
